--- a/spreadsheets/revised_cultures_GDGT_github_March2025_RR.xlsx
+++ b/spreadsheets/revised_cultures_GDGT_github_March2025_RR.xlsx
@@ -35,7 +35,7 @@
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
-    <author>RR</author>
+    <author> </author>
   </authors>
   <commentList>
     <comment ref="A73" authorId="0">
@@ -6155,7 +6155,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -6257,552 +6257,27 @@
               <c:f>master_cultures!$AK$2:$AK$189</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="188"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.32</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7</c:v>
+                  <c:v>0.12</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.7</c:v>
+                  <c:v>0.35</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.6</c:v>
+                  <c:v>0.26</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>7.5</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1.1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>5.3</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.4</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>14.4</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>10.5</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>8.8</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>31.2</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>12.2</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>7.5</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>25.2</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>15.2</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>12.1</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>5.78</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>5.04902735447094</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>6.37094346037539</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>4.62457465178225</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.098309617852306</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>4.94509613124634</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.210851371788283</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.0358314301205607</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.0857367320422929</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.16234894897708</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1.5837492047948</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.0827366341639229</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>9.13617310466401</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>11.9087203249125</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>6.23426348823763</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>5.71248837332884</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>15.9530645092725</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>1.740036068514</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>11.1934681427469</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>8.00289041732267</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>7.71104921632667</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>8.3309737133752</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>10.8214535020481</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>3.03620282220942</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>2.7378983060648</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>1.21453758477439</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.07</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.04</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.09</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0.32</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0.12</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>27.86</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>22.76</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>21.62</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>13.47</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>6.04</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>5.78</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>59.34</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>57.6</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>50.22</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>38.09</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>27.23</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>56.92</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>53.99</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>48.33</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>43.96</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>38.81</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>25.33</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>4.21</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>3.84</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>7.81</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>8.95</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>10.32</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>9.69</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>9.44</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>9.5</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>11.57</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>14.84</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>16.49</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>19.58</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>0.094736842</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>0.147368421</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>0.170212766</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>0.26</c:v>
-                </c:pt>
-                <c:pt idx="105">
                   <c:v>0.31</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>13.7</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>2.9</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>0.140728476821192</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>1.6</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>2.8</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>2.5</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>1.6</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>7.5</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>8.9</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>9.8</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>44.19</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>28.49</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>31.42</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>28.48</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>21.41</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>13.51</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>21.55</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>43.49</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>28.49</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>47.94</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>65.83</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>25.76</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>12.23</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>21.41</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>34.39</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>22.72</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>8.18</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>42.25</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>28.49</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>32.54</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>9.25</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>7.64</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>30.93</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>21.41</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>19.77</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>7.39</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>44.6</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>34.3</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>22.2</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>38.8</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>31.3</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>14.3</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>31.8</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>24.9</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>24.6</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>16.4</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>0.0646229223325278</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>0.0356433767201007</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>0.0279585536034026</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>0.00263948682698136</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>0.180956780264808</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>0.137989360708539</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>0.0904016926032679</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>0.0503399679097273</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>0.0960564048139003</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>0.353211590422786</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>0.259757471788775</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>0.160304967570937</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>0.104904844642111</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>0.242490573713855</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>0.515723727749872</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>0.437775323736155</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>0.379610207503242</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>0.34460612646573</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>0.514026471181191</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>0.408538178708186</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>0.340944371386148</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>0.363780848290774</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6865,540 +6340,27 @@
               <c:f>master_cultures!$AL$2:$AL$189</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="188"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0.6</c:v>
+                  <c:v>0.12</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3</c:v>
+                  <c:v>0.38</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1</c:v>
+                  <c:v>0.13</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.2</c:v>
+                  <c:v>0.14</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.4</c:v>
+                  <c:v>0.17</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1</c:v>
+                  <c:v>0.08</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.7</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.8</c:v>
-                </c:pt>
-                <c:pt idx="10">
                   <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>11.2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2.5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>3.9</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>4.8</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>8.4</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>9.6</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>7.1</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>18.4</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>9.6</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>5.9</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>17.1</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>12.6</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>4.71</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>2.38304386318605</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>6.93591665096578</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>4.19152266019089</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.0303562864445795</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>5.50368426360502</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>3.03555143227253</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.23898126836564</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>1.07027749656889</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.238167780132259</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1.3507600050849</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1.26332019975718</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>21.3281412183935</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>13.9406052504518</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>13.7911185322589</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>8.8853345276198</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>18.2243489884471</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>1.51144559681054</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>5.5869736662646</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>7.85348176649278</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>6.83330869608797</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>5.63503144788197</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>8.36065258280907</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.931464464588866</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>2.90178233001407</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>1.05027009197539</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.01</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.03</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0.02</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.06</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0.12</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0.38</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0.14</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>15.47</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>13.91</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>12.02</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>9.63</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>6.14</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>4.71</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>4.04</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>3.34</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>3.73</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>4.52</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>3.95</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>2.98</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>2.71</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>2.9</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>3.36</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>3.78</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>12.59</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>2.7</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>3.17</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>6.84</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>7.04</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>7.93</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>6.24</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>7.31</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>7.9</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>10.45</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>11.3</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>11.89</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>0.073684211</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>0.115789474</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>0.117021277</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>0.17</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>15.3</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>0.0894039735099339</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>1.2</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>6.6</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>8.57</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>7.62</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>10.91</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>11.45</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>11.08</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>5.76</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>6.08</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>8.57</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>6.29</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>10.78</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>8.25</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>7.85</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>11.45</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>10.93</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>13.31</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>4.69</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>7.34</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>8.57</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>10.63</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>8.76</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>5.9</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>10.72</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>11.45</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>14.14</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>9.73</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>20.1</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>19.2</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>23.1</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>20.1</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>10.8</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>14.2</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>8.7</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>5.9</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>5.5</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>8.5</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>6.1</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>0.0523565556535949</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>0.0309069050432531</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>0.02478284343528</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>0.00313795549274563</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>0.199728320954813</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>0.164472238241683</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>0.127243656682075</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>0.0730112414736814</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>0.108269850286558</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>0.126386708889941</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>0.132811792325685</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>0.118272341703722</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>0.091015958798162</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>0.199686089687055</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>0.133709782276437</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>0.174887305496125</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>0.177252789684837</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>0.180109248740323</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>0.0674529770714822</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>0.0417999212087021</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>0.0653029545206974</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>0.0461203751705111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7461,540 +6423,27 @@
               <c:f>master_cultures!$AM$2:$AM$189</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="188"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>2.8</c:v>
+                  <c:v>0.15</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9</c:v>
+                  <c:v>0.47</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.8</c:v>
+                  <c:v>0.17</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.8</c:v>
+                  <c:v>0.17</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.8</c:v>
+                  <c:v>0.11</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.7</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.4</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2.6</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.8</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>10.5</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6.5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6.4</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>3.4</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1.4</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1.5</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>14.2</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23.3</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>23.1</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>10.3</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>14.9</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>22.1</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>20.5</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>24.3</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>26.6</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>11.26</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1.94102985859028</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>11.4669961761064</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>3.73867356119331</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>2.97255022246746</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>7.38605458221894</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>16.8756513512623</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>6.19344356608915</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>13.2900320544714</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.39306706296659</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1.51835141371965</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>5.6848979614474</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>33.0981669730905</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>34.7569055700608</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>37.9251572728478</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>42.8659770775496</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>35.1010492141478</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>1.65522737678659</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>7.20902529491338</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>28.5180926519604</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>18.9034139296521</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>18.3290097685506</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>19.025379805967</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.388892306515647</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>3.4370446629403</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.267614631651405</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.23</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.04</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.06</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0.06</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.19</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.11</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0.47</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0.17</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0.17</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>8.57</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>10.84</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>7.32</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>9.37</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>11.97</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>11.26</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>2.09</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>1.88</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>2.37</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>2.71</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>1.97</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>1.34</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>1.46</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>1.53</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>1.41</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>1.46</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>5.53</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>16.6</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>16.26</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>14.84</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>13.43</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>12.42</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>25.58</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>18.37</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>15.82</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>12.62</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>10.81</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>7.69</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>0.210526316</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>0.178947368</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>0.159574468</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>0.11</c:v>
-                </c:pt>
-                <c:pt idx="105">
                   <c:v>0.09</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>14.3</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>3.4</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>0.107615894039735</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>7.5</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>7.5</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>0.8</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>0.8</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>22.97</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>27.83</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>23.92</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>36.34</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>37.83</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>39.72</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>27.11</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>21.15</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>27.83</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>19.76</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>15.15</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>32.27</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>36.33</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>37.83</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>36.24</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>35.99</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>24.48</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>25.09</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>27.83</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>33.09</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>34.66</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>30.32</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>36.11</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>37.83</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>42.23</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>38.42</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>7.8</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>10.4</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>10.1</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>11.2</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>13.2</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>12.3</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>13.2</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>9.1</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>12.2</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>8.6</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>8.8</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>0.0478738575680938</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>0.0314784922489127</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>0.0234857527861734</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>0.00386018079697568</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>0.135502368847285</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>0.133302080785347</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>0.180303173977843</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>0.168075053703548</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>0.153079000236393</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>0.0503652374005158</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>0.0621449691540855</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>0.0787746921634775</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>0.0849472274353484</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>0.154486790670343</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>0.0447452878654551</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>0.0621035722000656</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>0.0637082262388039</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>0.0870316320768309</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>0.0148935139910483</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>0.0150302757057933</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>0.0264680497246913</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>0.0177456459318475</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8057,543 +6506,27 @@
               <c:f>master_cultures!$AN$2:$AN$189</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="188"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>0.32</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.5</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.7</c:v>
+                  <c:v>0.38</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.8</c:v>
+                  <c:v>0.38</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.8</c:v>
+                  <c:v>0.01</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.4</c:v>
+                  <c:v>0.08</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.8</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>7.1</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>6.1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5.2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2.7</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>17.2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>12.5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>12.1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7.1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2.9</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>2.3</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>35.3</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>21.4</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>21.7</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>14.5</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>3.7</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>19.8</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>11.3</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>5.8</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>5.7</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>9.5</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>3.49</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1.38854964080314</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>6.22977037438213</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1.01574465748398</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>2.4007666386282</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>3.2070200763168</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>9.53491237332075</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>2.63231105867986</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>9.89834421653803</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.311164035699694</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1.29155650315485</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>4.28892587494397</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>7.86073630741743</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>12.5536085085512</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>11.6742320225314</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>17.7310886608243</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>11.9750907790281</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>1.45360610411551</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>10.3353490711655</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>8.0193165204347</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>9.61727166716602</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>16.4753277156183</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>18.0441974139864</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.206227154911585</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>3.78584670100164</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.894983202203262</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.01</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.25</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.14</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.14</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0.32</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0.38</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0.38</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>4.28</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>4.26</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>4.76</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>4.37</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>3.56</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>3.49</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>1.71</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>1.71</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>2.15</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>2.54</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>1.45</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>1.25</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>1.5</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>1.58</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>1.32</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>0.96</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>1.83</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>4.99</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>4.19</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>4.3</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>4.16</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>4.26</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>3.14</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>3.48</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>3.06</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>2.69</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>2.26</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>2.22</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>1.94</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>0.073684211</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>0.084210526</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>0.085106383</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>0.01</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="105">
                   <c:v>0.04</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>5.5</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>0.0695364238410596</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>7.6</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>5.1</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>5.1</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>1.1</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>1.2</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>0.4</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>1.5</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>5.69</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>9.73</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>9.39</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>8.01</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>11.78</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>13.26</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>8.94</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>7.15</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>9.73</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>6.42</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>2.76</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>9.09</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>14.97</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>11.78</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>7.22</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>11.09</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>12.68</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>8.01</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>9.73</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>8.8</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>15.75</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>12.84</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>8.96</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>11.78</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>10.81</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>16.08</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>2.4</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>2.9</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>3.3</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>3.2</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>3.2</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>4.3</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>2.9</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>2.9</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>4.6</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>2.2</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>3.2</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>4.2</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>0.0716534139217858</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>0.0593152981941857</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>0.0460937838894981</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>0.0126624164484942</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>0.0269325610224898</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>0.0238143841267373</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>0.0327481370330143</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>0.0323209839061975</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>0.0324967148172429</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>0.0394549225742002</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>0.0400965513427551</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>0.0404649548978106</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>0.0395471301091693</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>0.0886431015284976</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>0.020957003605465</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>0.0308621207053304</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>0.0443612245348016</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>0.0428271874079479</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>0.0127799295134205</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>0.00830115176078639</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>0.00928547359116495</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>0.00841077720521622</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8656,570 +6589,27 @@
               <c:f>master_cultures!$AO$2:$AO$189</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="188"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>29</c:v>
+                  <c:v>0.34</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19</c:v>
+                  <c:v>0.24</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>5.7</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.1</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2.8</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>4.9</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1.3</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>4.2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>3.5</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>49.1</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>47.1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>51</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>59</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>13.3</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>17.5</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>23.9</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>38.7</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>30.4</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>24.3</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>40.9</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>38.9</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>35.7</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>73.91</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>9.28033746611459</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>12.8456888541221</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>10.0772007105904</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>1.34691574227145</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>8.20805536108538</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1.09929708300875</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>8.84562794567547</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.886093421006641</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.0502496257963335</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.515838111871423</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>67.9684307748193</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>37.3193390485025</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.50322098997341</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>12.462341369751</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>14.5171495382647</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>11.9107409058</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>8.52350536654416</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>9.59443586354036</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>69.3488374272237</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>21.2734200502151</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>32.7299033907647</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>19.3213237470882</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>19.05277331908</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>19.3883281223896</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>12.8446284452577</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>45.1170017935372</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>57.301722590566</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>43.67</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>47.99</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>53.91</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>62.58</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>71.73</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>73.91</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>32.51</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>35.17</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>41.27</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>51.78</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>64.9</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>37.39</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>40.14</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>45.42</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>49.78</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>54.65</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>54.41</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>70.03</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>71.35</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>65.28</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>65.72</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>64.28</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>53.53</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>53.78</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>60.49</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>60.33</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>59.34</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>58.7</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>58.53</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>0.536842105</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>0.463157895</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>0.457446809</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>0.34</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>0.24</c:v>
-                </c:pt>
-                <c:pt idx="105">
                   <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>35.8</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>29.2</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>55.1</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>0.59271523178808</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>56</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>33.6</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>26.2</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>10.4</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>16.8</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>22.4</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>19.4</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>80.2</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>7.7</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>10.2</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>6.9</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>6.39</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>8.13</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>4.53</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>3.34</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>4.64</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>10.34</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>4.93</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>4.6</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>1.45</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>5.59</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>5.13</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>3.34</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>1.91</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>4.31</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>9.55</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>3.25</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>3.01</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>7.2</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>7.75</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>1.97</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>3.34</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>1.98</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>5.58</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>21.3</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>26.1</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>35.4</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>18.8</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>23.2</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>28.7</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>6.7</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>7.8</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>5.5</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>7.3</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>11.2</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>0.604613325377816</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>0.6306890688125</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>0.646853184616807</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>0.693758642691294</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>0.454031443867735</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>0.534842904411954</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>0.563224021312562</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>0.661357558508973</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>0.599388216966824</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>0.428238197467388</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>0.501219403861513</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>0.596275117453373</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>0.671876287742252</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>0.153446368557124</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>0.281868787062314</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>0.285259193446433</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>0.323836035743518</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>0.323895412656285</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>0.390847108242858</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>0.518682177492692</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>0.549092996365743</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>0.554988246525083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9282,468 +6672,27 @@
               <c:f>master_cultures!$AP$2:$AP$189</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="188"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.01</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>4.6</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1.3</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1.3</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>2.2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>4.9</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1.6</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1.2</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.4</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.84</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.454352984706014</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.411697930453323</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.223304363839989</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.325365558261136</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.184160276743516</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.961989060332397</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.713858403197846</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.612670355733102</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.322246769939556</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>1.13566668558685</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>5.48865179539637</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.705535009611373</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.747002661298785</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1.2013556460048</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.733944700392879</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>1.18529342417239</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>1.46103224384799</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.480775973103059</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>1.47651038672734</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>2.33301887781494</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.647351192666829</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>1.69021658366129</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1.79981704402652</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>1.18793252997312</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.879579105586369</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>26.4104190822172</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>28.9621293737269</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>0.24</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>0.37</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>0.58</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>0.56</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>0.84</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>0.31</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>0.26</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>0.36</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>0.12</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>0.23</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>0.17</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>0.34</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>0.31</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>1.28</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>1.18</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>0.89</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>0.62</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>0.61</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>0.37</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>0.36</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>0.64</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>0.55</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>0.43</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>0.39</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>0.29</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>0.010526316</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>0.010526316</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>0.010638298</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>0.004</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>0.01</c:v>
-                </c:pt>
-                <c:pt idx="105">
                   <c:v>0.006</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>1.1</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>13.7</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>22.9</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>1.1</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>1.2</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>0.4</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>0.0790791940219373</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>0.110109770635775</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>0.117210880046558</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>0.165552707354349</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>0.00284852504287042</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>0.00557903172573946</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>0.00607931839123843</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>0.014895194497873</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>0.0107098128790818</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>0.00234334324517002</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>0.00396981152718629</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>0.00590792621067985</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>0.00770855127295782</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>0.161247075843126</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>0.0029954114404571</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>0.00911248441589158</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>0.011231516294797</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>0.0215303926528836</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>0.00226053992117042</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>0.00294973328276556</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>0.00260172179470324</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9751,11 +6700,11 @@
         </c:ser>
         <c:gapWidth val="0"/>
         <c:overlap val="100"/>
-        <c:axId val="94718577"/>
-        <c:axId val="28750264"/>
+        <c:axId val="36825987"/>
+        <c:axId val="39180298"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="94718577"/>
+        <c:axId val="36825987"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9787,7 +6736,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28750264"/>
+        <c:crossAx val="39180298"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9795,7 +6744,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28750264"/>
+        <c:axId val="39180298"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9834,7 +6783,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94718577"/>
+        <c:crossAx val="36825987"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9886,7 +6835,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -10470,11 +7419,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="95402069"/>
-        <c:axId val="34512991"/>
+        <c:axId val="2537942"/>
+        <c:axId val="17495577"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="95402069"/>
+        <c:axId val="2537942"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10550,12 +7499,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34512991"/>
+        <c:crossAx val="17495577"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="34512991"/>
+        <c:axId val="17495577"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10631,7 +7580,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95402069"/>
+        <c:crossAx val="2537942"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -10683,7 +7632,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -11241,11 +8190,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="89982003"/>
-        <c:axId val="26858484"/>
+        <c:axId val="22472975"/>
+        <c:axId val="67769054"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="89982003"/>
+        <c:axId val="22472975"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11321,12 +8270,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26858484"/>
+        <c:crossAx val="67769054"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="26858484"/>
+        <c:axId val="67769054"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11402,7 +8351,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89982003"/>
+        <c:crossAx val="22472975"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -11465,9 +8414,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>476640</xdr:colOff>
+      <xdr:colOff>476280</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>88920</xdr:rowOff>
+      <xdr:rowOff>88560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -11476,7 +8425,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="8637840" cy="6266160"/>
+        <a:ext cx="7669440" cy="6265800"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -11504,9 +8453,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>469800</xdr:colOff>
+      <xdr:colOff>469440</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>77040</xdr:rowOff>
+      <xdr:rowOff>76680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -11515,7 +8464,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="8631000" cy="6254280"/>
+        <a:ext cx="7662600" cy="6253920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -11539,9 +8488,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>475560</xdr:colOff>
+      <xdr:colOff>475200</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>86400</xdr:rowOff>
+      <xdr:rowOff>86040</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -11550,7 +8499,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="8636760" cy="6263640"/>
+        <a:ext cx="7668360" cy="6263280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -29155,6 +26104,117 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="0" compactData="0">
+  <location ref="A3:C18" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="74">
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField axis="axisCol" compact="0" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" showAll="0">
+      <items count="14">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="62"/>
+  </rowFields>
+  <colFields count="1">
+    <field x="24"/>
+  </colFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="DataPilot1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="0" compactData="0">
   <location ref="A4:D41" firstHeaderRow="1" firstDataRow="1" firstDataCol="3" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="74">
@@ -29322,120 +26382,21 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="0" compactData="0">
-  <location ref="A3:C18" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="74">
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField axis="axisCol" compact="0" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" showAll="0">
-      <items count="14">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="62"/>
-  </rowFields>
-  <colFields count="1">
-    <field x="24"/>
-  </colFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:BV209" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:BV209"/>
+  <autoFilter ref="A1:BV209">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Pitcher2010_001_ThAOA cultures-Ca. Nitrososphaera gargensis-Ga9.2_46a"/>
+        <filter val="Pitcher2010_002_ThAOA cultures-Ca. Nitrososphaera gargensis-Ga9.2_42"/>
+        <filter val="Pitcher2010_003_ThAOA cultures-Ca. Nitrososphaera gargensis-Ga9.2_50"/>
+        <filter val="Pitcher2010_004_ThAOA cultures-Ca. Nitrososphaera gargensis-Ga9.2_46"/>
+        <filter val="Pitcher2011_AR1_T25_pH8.2"/>
+        <filter val="Pitcher2011_Ca Nitrosoarchaeum limnia SFB1_T22_pH"/>
+        <filter val="Pitcher2011_SJ_T25_pH8.2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="74">
     <tableColumn id="1" name="sampleName"/>
     <tableColumn id="2" name="Strains"/>
@@ -29524,8 +26485,8 @@
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.28"/>
   </cols>
   <sheetData>
@@ -30091,7 +27052,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -30122,14 +27083,14 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="48.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="34" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="17.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="17.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="34" width="51.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="37.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="35" width="19.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="35" width="21.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="35" width="22.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="35" width="22.76"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31901,7 +28862,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="35" style="1" width="16.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="51" width="16.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="51" width="8.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="51" width="8.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="51" width="8.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="51" width="7.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="51" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="51" width="20.14"/>
@@ -31909,7 +28870,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="52" style="51" width="11.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="59" style="1" width="16.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="60" style="1" width="18.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="61" style="1" width="56.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="61" style="1" width="56.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="34" width="35.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="63" style="1" width="64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="66" style="1" width="13.93"/>
@@ -31919,10 +28880,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="71" style="1" width="28.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="72" min="72" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="73" min="73" style="1" width="38.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="74" min="74" style="1" width="54.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="74" min="74" style="1" width="54.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="79" min="79" style="1" width="20.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="81" min="81" style="1" width="39.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="82" min="82" style="1" width="54.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="82" min="82" style="1" width="54.85"/>
   </cols>
   <sheetData>
     <row r="1" s="57" customFormat="true" ht="216.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32149,7 +29110,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="37" t="s">
         <v>388</v>
       </c>
@@ -32342,7 +29303,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="37" t="s">
         <v>408</v>
       </c>
@@ -32535,7 +29496,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="37" t="s">
         <v>411</v>
       </c>
@@ -32728,7 +29689,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="37" t="s">
         <v>413</v>
       </c>
@@ -32921,7 +29882,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="37" t="s">
         <v>416</v>
       </c>
@@ -33114,7 +30075,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="37" t="s">
         <v>418</v>
       </c>
@@ -33307,7 +30268,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="37" t="s">
         <v>420</v>
       </c>
@@ -33500,7 +30461,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="37" t="s">
         <v>423</v>
       </c>
@@ -33693,7 +30654,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="37" t="s">
         <v>425</v>
       </c>
@@ -33886,7 +30847,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="37" t="s">
         <v>427</v>
       </c>
@@ -34079,7 +31040,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
         <v>430</v>
       </c>
@@ -34272,7 +31233,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="37" t="s">
         <v>432</v>
       </c>
@@ -34465,7 +31426,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="37" t="s">
         <v>434</v>
       </c>
@@ -34658,7 +31619,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="37" t="s">
         <v>437</v>
       </c>
@@ -34851,7 +31812,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
         <v>439</v>
       </c>
@@ -35044,7 +32005,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
         <v>441</v>
       </c>
@@ -35237,7 +32198,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="37" t="s">
         <v>444</v>
       </c>
@@ -35430,7 +32391,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
         <v>446</v>
       </c>
@@ -35623,7 +32584,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="37" t="s">
         <v>448</v>
       </c>
@@ -35818,7 +32779,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
         <v>453</v>
       </c>
@@ -36013,7 +32974,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="37" t="s">
         <v>455</v>
       </c>
@@ -36208,7 +33169,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
         <v>457</v>
       </c>
@@ -36407,7 +33368,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="37" t="s">
         <v>469</v>
       </c>
@@ -36606,7 +33567,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="37" t="s">
         <v>471</v>
       </c>
@@ -36805,7 +33766,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="37" t="s">
         <v>473</v>
       </c>
@@ -37004,7 +33965,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
         <v>475</v>
       </c>
@@ -37203,7 +34164,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="37" t="s">
         <v>477</v>
       </c>
@@ -37402,7 +34363,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="37" t="s">
         <v>479</v>
       </c>
@@ -37601,7 +34562,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="37" t="s">
         <v>481</v>
       </c>
@@ -37804,7 +34765,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="37" t="s">
         <v>484</v>
       </c>
@@ -38007,7 +34968,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="37" t="s">
         <v>486</v>
       </c>
@@ -38210,7 +35171,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="37" t="s">
         <v>488</v>
       </c>
@@ -38411,7 +35372,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="37" t="s">
         <v>490</v>
       </c>
@@ -38614,7 +35575,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="37" t="s">
         <v>496</v>
       </c>
@@ -38817,7 +35778,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="37" t="s">
         <v>498</v>
       </c>
@@ -39020,7 +35981,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="37" t="s">
         <v>501</v>
       </c>
@@ -39219,7 +36180,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="37" t="s">
         <v>503</v>
       </c>
@@ -39418,7 +36379,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="37" t="s">
         <v>505</v>
       </c>
@@ -39621,7 +36582,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="37" t="s">
         <v>507</v>
       </c>
@@ -39824,7 +36785,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
         <v>509</v>
       </c>
@@ -40027,7 +36988,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
         <v>511</v>
       </c>
@@ -40226,7 +37187,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="37" t="s">
         <v>513</v>
       </c>
@@ -40425,7 +37386,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="37" t="s">
         <v>515</v>
       </c>
@@ -40620,7 +37581,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="37" t="s">
         <v>521</v>
       </c>
@@ -40817,7 +37778,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="37" t="s">
         <v>525</v>
       </c>
@@ -41014,7 +37975,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="37" t="s">
         <v>527</v>
       </c>
@@ -41217,7 +38178,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="37" t="s">
         <v>529</v>
       </c>
@@ -41420,7 +38381,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="37" t="s">
         <v>531</v>
       </c>
@@ -41623,7 +38584,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="37" t="s">
         <v>533</v>
       </c>
@@ -41822,7 +38783,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="37" t="s">
         <v>535</v>
       </c>
@@ -42021,7 +38982,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="37" t="s">
         <v>537</v>
       </c>
@@ -42218,7 +39179,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="37" t="s">
         <v>539</v>
       </c>
@@ -42421,7 +39382,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="37" t="s">
         <v>542</v>
       </c>
@@ -42624,7 +39585,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="37" t="s">
         <v>544</v>
       </c>
@@ -42827,7 +39788,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="37" t="s">
         <v>546</v>
       </c>
@@ -43026,7 +39987,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="37" t="s">
         <v>548</v>
       </c>
@@ -43225,7 +40186,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="37" t="s">
         <v>551</v>
       </c>
@@ -43420,7 +40381,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="37" t="s">
         <v>553</v>
       </c>
@@ -43617,7 +40578,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="37" t="s">
         <v>555</v>
       </c>
@@ -43814,7 +40775,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="61" s="63" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" s="63" customFormat="true" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="49" t="s">
         <v>557</v>
       </c>
@@ -44025,7 +40986,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="62" s="63" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" s="63" customFormat="true" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="49" t="s">
         <v>569</v>
       </c>
@@ -44238,7 +41199,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="63" s="63" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" s="63" customFormat="true" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
         <v>573</v>
       </c>
@@ -44441,7 +41402,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="64" s="63" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" s="63" customFormat="true" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
         <v>576</v>
       </c>
@@ -44646,7 +41607,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="65" s="63" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" s="63" customFormat="true" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="49" t="s">
         <v>579</v>
       </c>
@@ -44849,7 +41810,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="66" s="63" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" s="63" customFormat="true" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="49" t="s">
         <v>584</v>
       </c>
@@ -45052,7 +42013,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="67" s="63" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" s="63" customFormat="true" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="49" t="s">
         <v>587</v>
       </c>
@@ -45255,7 +42216,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="68" s="63" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" s="63" customFormat="true" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="49" t="s">
         <v>591</v>
       </c>
@@ -46238,7 +43199,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="37" t="s">
         <v>606</v>
       </c>
@@ -46439,7 +43400,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="37" t="s">
         <v>610</v>
       </c>
@@ -46640,7 +43601,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="37" t="s">
         <v>612</v>
       </c>
@@ -46841,7 +43802,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="37" t="s">
         <v>614</v>
       </c>
@@ -47042,7 +44003,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="37" t="s">
         <v>616</v>
       </c>
@@ -47243,7 +44204,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="37" t="s">
         <v>618</v>
       </c>
@@ -47444,7 +44405,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="37" t="s">
         <v>620</v>
       </c>
@@ -47637,7 +44598,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="37" t="s">
         <v>622</v>
       </c>
@@ -47830,7 +44791,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="37" t="s">
         <v>624</v>
       </c>
@@ -48023,7 +44984,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="37" t="s">
         <v>626</v>
       </c>
@@ -48216,7 +45177,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="37" t="s">
         <v>628</v>
       </c>
@@ -48409,7 +45370,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="37" t="s">
         <v>630</v>
       </c>
@@ -48602,7 +45563,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="37" t="s">
         <v>632</v>
       </c>
@@ -48795,7 +45756,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="37" t="s">
         <v>634</v>
       </c>
@@ -48988,7 +45949,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="37" t="s">
         <v>636</v>
       </c>
@@ -49181,7 +46142,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="37" t="s">
         <v>638</v>
       </c>
@@ -49374,7 +46335,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="37" t="s">
         <v>640</v>
       </c>
@@ -49575,7 +46536,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="37" t="s">
         <v>644</v>
       </c>
@@ -49776,7 +46737,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="37" t="s">
         <v>647</v>
       </c>
@@ -49977,7 +46938,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="37" t="s">
         <v>649</v>
       </c>
@@ -50178,7 +47139,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="37" t="s">
         <v>651</v>
       </c>
@@ -50379,7 +47340,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="37" t="s">
         <v>653</v>
       </c>
@@ -50580,7 +47541,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="37" t="s">
         <v>655</v>
       </c>
@@ -50781,7 +47742,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="37" t="s">
         <v>657</v>
       </c>
@@ -50982,7 +47943,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="37" t="s">
         <v>659</v>
       </c>
@@ -51183,7 +48144,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="37" t="s">
         <v>661</v>
       </c>
@@ -51384,7 +48345,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="37" t="s">
         <v>663</v>
       </c>
@@ -51585,7 +48546,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="37" t="s">
         <v>665</v>
       </c>
@@ -51786,7 +48747,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="37" t="s">
         <v>667</v>
       </c>
@@ -51987,7 +48948,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="37" t="s">
         <v>669</v>
       </c>
@@ -52190,7 +49151,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="37" t="s">
         <v>677</v>
       </c>
@@ -52393,7 +49354,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="37" t="s">
         <v>680</v>
       </c>
@@ -53195,7 +50156,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="37" t="s">
         <v>697</v>
       </c>
@@ -53390,7 +50351,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="37" t="s">
         <v>704</v>
       </c>
@@ -53581,7 +50542,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="37" t="s">
         <v>706</v>
       </c>
@@ -53776,7 +50737,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="31.3" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="37" t="s">
         <v>709</v>
       </c>
@@ -53977,7 +50938,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="31.3" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="37" t="s">
         <v>717</v>
       </c>
@@ -54166,7 +51127,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="31.3" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="37" t="s">
         <v>724</v>
       </c>
@@ -54361,7 +51322,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="31.3" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="37" t="s">
         <v>728</v>
       </c>
@@ -54550,7 +51511,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="31.3" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="37" t="s">
         <v>733</v>
       </c>
@@ -54741,7 +51702,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="37" t="s">
         <v>739</v>
       </c>
@@ -54944,7 +51905,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="37" t="s">
         <v>748</v>
       </c>
@@ -55147,7 +52108,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="37" t="s">
         <v>750</v>
       </c>
@@ -55350,7 +52311,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="37" t="s">
         <v>752</v>
       </c>
@@ -55553,7 +52514,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="37" t="s">
         <v>754</v>
       </c>
@@ -55746,7 +52707,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="37" t="s">
         <v>757</v>
       </c>
@@ -55945,7 +52906,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="37" t="s">
         <v>759</v>
       </c>
@@ -56138,7 +53099,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="37" t="s">
         <v>761</v>
       </c>
@@ -56335,7 +53296,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="37" t="s">
         <v>763</v>
       </c>
@@ -56528,7 +53489,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="37" t="s">
         <v>766</v>
       </c>
@@ -56721,7 +53682,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="37" t="s">
         <v>768</v>
       </c>
@@ -56914,7 +53875,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="37" t="s">
         <v>770</v>
       </c>
@@ -57107,7 +54068,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="37" t="s">
         <v>772</v>
       </c>
@@ -57300,7 +54261,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="37" t="s">
         <v>774</v>
       </c>
@@ -57493,7 +54454,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="37" t="s">
         <v>776</v>
       </c>
@@ -57688,7 +54649,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="37" t="s">
         <v>787</v>
       </c>
@@ -57883,7 +54844,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="37" t="s">
         <v>789</v>
       </c>
@@ -58078,7 +55039,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="37" t="s">
         <v>791</v>
       </c>
@@ -58273,7 +55234,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="37" t="s">
         <v>793</v>
       </c>
@@ -58468,7 +55429,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="37" t="s">
         <v>795</v>
       </c>
@@ -58663,7 +55624,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="37" t="s">
         <v>797</v>
       </c>
@@ -58857,7 +55818,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="37" t="s">
         <v>799</v>
       </c>
@@ -59051,7 +56012,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="37" t="s">
         <v>787</v>
       </c>
@@ -59245,7 +56206,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="37" t="s">
         <v>802</v>
       </c>
@@ -59439,7 +56400,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="37" t="s">
         <v>804</v>
       </c>
@@ -59633,7 +56594,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="37" t="s">
         <v>806</v>
       </c>
@@ -59827,7 +56788,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="37" t="s">
         <v>808</v>
       </c>
@@ -60021,7 +56982,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="37" t="s">
         <v>793</v>
       </c>
@@ -60215,7 +57176,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="37" t="s">
         <v>811</v>
       </c>
@@ -60409,7 +57370,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="37" t="s">
         <v>813</v>
       </c>
@@ -60603,7 +57564,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="37" t="s">
         <v>815</v>
       </c>
@@ -60798,7 +57759,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="37" t="s">
         <v>818</v>
       </c>
@@ -60993,7 +57954,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="37" t="s">
         <v>787</v>
       </c>
@@ -61188,7 +58149,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="37" t="s">
         <v>822</v>
       </c>
@@ -61383,7 +58344,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="37" t="s">
         <v>825</v>
       </c>
@@ -61578,7 +58539,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="37" t="s">
         <v>828</v>
       </c>
@@ -61773,7 +58734,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="37" t="s">
         <v>830</v>
       </c>
@@ -61968,7 +58929,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="37" t="s">
         <v>793</v>
       </c>
@@ -62163,7 +59124,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="37" t="s">
         <v>833</v>
       </c>
@@ -62358,7 +59319,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="37" t="s">
         <v>835</v>
       </c>
@@ -62553,7 +59514,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="37" t="s">
         <v>837</v>
       </c>
@@ -62756,7 +59717,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="37" t="s">
         <v>845</v>
       </c>
@@ -62959,7 +59920,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="37" t="s">
         <v>847</v>
       </c>
@@ -63162,7 +60123,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="37" t="s">
         <v>849</v>
       </c>
@@ -63365,7 +60326,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="37" t="s">
         <v>851</v>
       </c>
@@ -63568,7 +60529,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="37" t="s">
         <v>853</v>
       </c>
@@ -63771,7 +60732,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="37" t="s">
         <v>855</v>
       </c>
@@ -63974,7 +60935,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="37" t="s">
         <v>857</v>
       </c>
@@ -64177,7 +61138,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="37" t="s">
         <v>859</v>
       </c>
@@ -64380,7 +61341,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="37" t="s">
         <v>861</v>
       </c>
@@ -64583,7 +61544,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="37" t="s">
         <v>863</v>
       </c>
@@ -64786,7 +61747,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="37" t="s">
         <v>865</v>
       </c>
@@ -64989,7 +61950,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="37" t="s">
         <v>867</v>
       </c>
@@ -65184,7 +62145,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="37" t="s">
         <v>872</v>
       </c>
@@ -65379,7 +62340,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="37" t="s">
         <v>874</v>
       </c>
@@ -65574,7 +62535,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="37" t="s">
         <v>876</v>
       </c>
@@ -65769,7 +62730,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="37" t="s">
         <v>878</v>
       </c>
@@ -65964,7 +62925,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="37" t="s">
         <v>880</v>
       </c>
@@ -66159,7 +63120,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="37" t="s">
         <v>882</v>
       </c>
@@ -66354,7 +63315,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="37" t="s">
         <v>884</v>
       </c>
@@ -66549,7 +63510,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="37" t="s">
         <v>886</v>
       </c>
@@ -66744,7 +63705,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="37" t="s">
         <v>888</v>
       </c>
@@ -66943,7 +63904,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="37" t="s">
         <v>890</v>
       </c>
@@ -67142,7 +64103,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="37" t="s">
         <v>892</v>
       </c>
@@ -67341,7 +64302,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="37" t="s">
         <v>894</v>
       </c>
@@ -67540,7 +64501,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="37" t="s">
         <v>896</v>
       </c>
@@ -67727,7 +64688,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="37" t="s">
         <v>903</v>
       </c>
@@ -67926,7 +64887,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="37" t="s">
         <v>905</v>
       </c>
@@ -68125,7 +65086,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="37" t="s">
         <v>907</v>
       </c>
@@ -68324,7 +65285,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="37" t="s">
         <v>909</v>
       </c>
@@ -68523,7 +65484,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="37" t="s">
         <v>912</v>
       </c>
@@ -68722,7 +65683,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="37" t="s">
         <v>921</v>
       </c>
@@ -68921,7 +65882,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="37" t="s">
         <v>923</v>
       </c>
@@ -69120,7 +66081,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="37" t="s">
         <v>925</v>
       </c>
@@ -69319,7 +66280,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
         <v>927</v>
       </c>
@@ -69507,7 +66468,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
         <v>935</v>
       </c>
@@ -69695,7 +66656,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
         <v>937</v>
       </c>
@@ -69883,7 +66844,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
         <v>939</v>
       </c>
@@ -70071,7 +67032,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
         <v>941</v>
       </c>
@@ -70259,7 +67220,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
         <v>943</v>
       </c>
@@ -70447,7 +67408,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
         <v>945</v>
       </c>
@@ -70635,7 +67596,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
         <v>947</v>
       </c>
@@ -70823,7 +67784,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
         <v>949</v>
       </c>
@@ -71011,7 +67972,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
         <v>951</v>
       </c>
@@ -71199,7 +68160,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="16.4" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
         <v>953</v>
       </c>
@@ -71387,7 +68348,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
         <v>956</v>
       </c>
@@ -71575,7 +68536,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
         <v>958</v>
       </c>
@@ -71763,7 +68724,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
         <v>960</v>
       </c>
@@ -71951,7 +68912,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
         <v>962</v>
       </c>
@@ -72139,7 +69100,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
         <v>964</v>
       </c>
@@ -72327,7 +69288,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
         <v>966</v>
       </c>
@@ -72515,7 +69476,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
         <v>968</v>
       </c>
@@ -72703,7 +69664,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
         <v>970</v>
       </c>
@@ -72891,7 +69852,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="17.7" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
         <v>972</v>
       </c>
@@ -73177,7 +70138,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -73196,7 +70157,7 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/spreadsheets/revised_cultures_GDGT_github_March2025_RR.xlsx
+++ b/spreadsheets/revised_cultures_GDGT_github_March2025_RR.xlsx
@@ -2784,7 +2784,7 @@
     <t xml:space="preserve">Feyhl-Buska2016_Picrophilus torridus_Culture-C-GDGT_T53_pH0.7_growthLog</t>
   </si>
   <si>
-    <t xml:space="preserve">Picrophilus torridus</t>
+    <t xml:space="preserve">Picrophilus torridus DSM 9790</t>
   </si>
   <si>
     <t xml:space="preserve">p__Thermoplasmatota</t>
@@ -6330,7 +6330,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -6432,549 +6432,84 @@
               <c:f>master_cultures!$AL$2:$AL$188</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="187"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>44.19</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>28.49</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>31.42</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7</c:v>
+                  <c:v>28.48</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.7</c:v>
+                  <c:v>21.41</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.6</c:v>
+                  <c:v>13.51</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.5</c:v>
+                  <c:v>21.55</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2</c:v>
+                  <c:v>43.49</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.5</c:v>
+                  <c:v>28.49</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>47.94</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>65.83</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>25.76</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>12.23</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>21.41</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>34.39</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>7.5</c:v>
+                  <c:v>22.72</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.9</c:v>
+                  <c:v>8.18</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.1</c:v>
+                  <c:v>42.25</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.3</c:v>
+                  <c:v>28.49</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.4</c:v>
+                  <c:v>32.54</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.5</c:v>
+                  <c:v>9.25</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>10</c:v>
+                  <c:v>7.64</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>14.4</c:v>
+                  <c:v>30.93</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>10.5</c:v>
+                  <c:v>21.41</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8.8</c:v>
+                  <c:v>19.77</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>31.2</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>12.2</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>7.5</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>25.2</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>15.2</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>12.1</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>5.04902735447094</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>6.37094346037539</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>4.62457465178225</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.098309617852306</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>4.94509613124634</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.210851371788283</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.0358314301205607</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.0857367320422929</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.16234894897708</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1.5837492047948</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.0827366341639229</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>9.13617310466401</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>11.9087203249125</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>6.23426348823763</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>5.71248837332884</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>15.9530645092725</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>1.740036068514</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>11.1934681427469</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>8.00289041732267</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>7.71104921632667</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>8.3309737133752</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>10.8214535020481</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>3.03620282220942</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>2.7378983060648</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>1.21453758477439</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.07</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.04</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0.09</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0.32</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0.12</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>27.86</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>22.76</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>21.62</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>13.47</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>6.04</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>5.78</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>59.34</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>57.6</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>50.22</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>38.09</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>27.23</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>56.92</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>53.99</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>48.33</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>43.96</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>38.81</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>25.33</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>4.21</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>3.84</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>7.81</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>8.95</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>10.32</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>9.69</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>9.44</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>9.5</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>11.57</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>14.84</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>16.49</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>19.58</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>0.094736842</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>0.147368421</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>0.170212766</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>0.26</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>0.31</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>13.7</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>2.9</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>0.140728476821192</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>1.6</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>2.8</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>2.5</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>1.6</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>7.5</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>8.9</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>9.8</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>44.19</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>28.49</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>31.42</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>28.48</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>21.41</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>13.51</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>21.55</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>43.49</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>28.49</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>47.94</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>65.83</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>25.76</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>12.23</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>21.41</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>34.39</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>22.72</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>8.18</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>42.25</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>28.49</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>32.54</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>9.25</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>7.64</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>30.93</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>21.41</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>19.77</c:v>
-                </c:pt>
-                <c:pt idx="152">
                   <c:v>7.39</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>44.6</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>34.3</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>22.2</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>38.8</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>31.3</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>14.3</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>31.8</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>24.9</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>23.4</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>24.6</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>16.4</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>0.0646229223325278</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>0.0356433767201007</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>0.0279585536034026</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>0.00263948682698136</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>0.180956780264808</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>0.137989360708539</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>0.0904016926032679</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>0.0503399679097273</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>0.0960564048139003</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>0.353211590422786</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>0.259757471788775</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>0.160304967570937</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>0.104904844642111</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>0.242490573713855</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>0.515723727749872</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>0.437775323736155</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>0.379610207503242</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>0.34460612646573</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>0.514026471181191</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>0.408538178708186</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>0.340944371386148</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>0.363780848290774</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7037,537 +6572,84 @@
               <c:f>master_cultures!$AM$2:$AM$188</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="187"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0.6</c:v>
+                  <c:v>6.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3</c:v>
+                  <c:v>8.57</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1</c:v>
+                  <c:v>7.62</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.2</c:v>
+                  <c:v>10.91</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.4</c:v>
+                  <c:v>11.45</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1</c:v>
+                  <c:v>11.08</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.6</c:v>
+                  <c:v>5.76</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.7</c:v>
+                  <c:v>6.08</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.9</c:v>
+                  <c:v>8.57</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.8</c:v>
+                  <c:v>6.29</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1</c:v>
+                  <c:v>10.78</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>8.25</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>7.85</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>11.45</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>10.93</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>11.2</c:v>
+                  <c:v>13.31</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.5</c:v>
+                  <c:v>4.69</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2</c:v>
+                  <c:v>7.34</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>11</c:v>
+                  <c:v>8.57</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3.9</c:v>
+                  <c:v>10.63</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4.8</c:v>
+                  <c:v>8.76</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>8.4</c:v>
+                  <c:v>5.9</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>9.6</c:v>
+                  <c:v>10.72</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>7.1</c:v>
+                  <c:v>11.45</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7</c:v>
+                  <c:v>14.14</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>18.4</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>9.6</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>5.9</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>17.1</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>12.6</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>2.38304386318605</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>6.93591665096578</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>4.19152266019089</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.0303562864445795</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>5.50368426360502</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>3.03555143227253</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.23898126836564</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>1.07027749656889</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.238167780132259</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1.3507600050849</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1.26332019975718</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>21.3281412183935</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>13.9406052504518</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>13.7911185322589</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>8.8853345276198</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>18.2243489884471</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>1.51144559681054</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>5.5869736662646</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>7.85348176649278</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>6.83330869608797</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>5.63503144788197</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>8.36065258280907</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.931464464588866</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>2.90178233001407</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>1.05027009197539</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.01</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.03</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.02</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.06</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.12</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0.38</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0.14</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>15.47</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>13.91</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>12.02</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>9.63</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>6.14</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>4.71</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>4.04</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>3.34</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>3.73</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>4.52</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>3.95</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>2.98</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>2.71</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>2.9</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>3.36</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>3.78</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>12.59</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>2.7</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>3.17</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>6.84</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>7.04</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>7.93</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>6.24</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>7.31</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>7.9</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>10.45</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>11.3</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>11.89</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>0.073684211</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>0.115789474</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>0.117021277</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>0.17</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>15.3</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>0.0894039735099339</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>1.2</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>6.6</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>8.57</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>7.62</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>10.91</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>11.45</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>11.08</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>5.76</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>6.08</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>8.57</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>6.29</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>10.78</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>8.25</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>7.85</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>11.45</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>10.93</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>13.31</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>4.69</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>7.34</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>8.57</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>10.63</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>8.76</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>5.9</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>10.72</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>11.45</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>14.14</c:v>
-                </c:pt>
-                <c:pt idx="152">
                   <c:v>9.73</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>20.1</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>19.2</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>23.1</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>20.1</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>10.8</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>14.2</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>8.7</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>5.9</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>5.5</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>8.5</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>6.1</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>0.0523565556535949</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>0.0309069050432531</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>0.02478284343528</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>0.00313795549274563</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>0.199728320954813</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>0.164472238241683</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>0.127243656682075</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>0.0730112414736814</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>0.108269850286558</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>0.126386708889941</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>0.132811792325685</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>0.118272341703722</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>0.091015958798162</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>0.199686089687055</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>0.133709782276437</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>0.174887305496125</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>0.177252789684837</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>0.180109248740323</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>0.0674529770714822</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>0.0417999212087021</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>0.0653029545206974</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>0.0461203751705111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7630,537 +6712,84 @@
               <c:f>master_cultures!$AN$2:$AN$188</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="187"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>2.8</c:v>
+                  <c:v>22.97</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9</c:v>
+                  <c:v>27.83</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.8</c:v>
+                  <c:v>23.92</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.8</c:v>
+                  <c:v>36.34</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3</c:v>
+                  <c:v>37.83</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.8</c:v>
+                  <c:v>39.72</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.5</c:v>
+                  <c:v>27.11</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.7</c:v>
+                  <c:v>21.15</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1</c:v>
+                  <c:v>27.83</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.4</c:v>
+                  <c:v>19.76</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.6</c:v>
+                  <c:v>15.15</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.8</c:v>
+                  <c:v>32.27</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>36.33</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>37.83</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>36.24</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>10.5</c:v>
+                  <c:v>35.99</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>6.5</c:v>
+                  <c:v>24.48</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>6.4</c:v>
+                  <c:v>25.09</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3.4</c:v>
+                  <c:v>27.83</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.4</c:v>
+                  <c:v>33.09</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.5</c:v>
+                  <c:v>34.66</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>14.2</c:v>
+                  <c:v>30.32</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>23.3</c:v>
+                  <c:v>36.11</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>23.1</c:v>
+                  <c:v>37.83</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>10.3</c:v>
+                  <c:v>42.23</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>14.9</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>22.1</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>20.5</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>24.3</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>26.6</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1.94102985859028</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>11.4669961761064</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>3.73867356119331</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>2.97255022246746</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>7.38605458221894</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>16.8756513512623</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>6.19344356608915</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>13.2900320544714</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.39306706296659</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1.51835141371965</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>5.6848979614474</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>33.0981669730905</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>34.7569055700608</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>37.9251572728478</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>42.8659770775496</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>35.1010492141478</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>1.65522737678659</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>7.20902529491338</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>28.5180926519604</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>18.9034139296521</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>18.3290097685506</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>19.025379805967</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.388892306515647</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>3.4370446629403</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.267614631651405</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.23</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.04</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.06</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.06</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0.19</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.11</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0.47</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0.17</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0.17</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>8.57</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>10.84</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>7.32</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>9.37</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>11.97</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>11.26</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>2.09</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>1.88</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>2.37</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>2.71</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>1.97</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>1.34</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>1.46</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>1.53</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>1.41</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>1.46</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>5.53</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>16.6</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>16.26</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>14.84</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>13.43</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>12.42</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>25.58</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>18.37</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>15.82</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>12.62</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>10.81</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>7.69</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>0.210526316</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>0.178947368</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>0.159574468</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>0.11</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>0.09</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>14.3</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>3.4</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>0.107615894039735</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>7.5</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>7.5</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>0.8</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>0.8</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>22.97</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>27.83</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>23.92</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>36.34</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>37.83</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>39.72</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>27.11</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>21.15</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>27.83</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>19.76</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>15.15</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>32.27</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>36.33</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>37.83</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>36.24</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>35.99</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>24.48</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>25.09</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>27.83</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>33.09</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>34.66</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>30.32</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>36.11</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>37.83</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>42.23</c:v>
-                </c:pt>
-                <c:pt idx="152">
                   <c:v>38.42</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>7.8</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>10.4</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>10.1</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>11.2</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>13.2</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>12.3</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>13.2</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>9.1</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>12.2</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>8.6</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>8.8</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>0.0478738575680938</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>0.0314784922489127</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>0.0234857527861734</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>0.00386018079697568</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>0.135502368847285</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>0.133302080785347</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>0.180303173977843</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>0.168075053703548</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>0.153079000236393</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>0.0503652374005158</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>0.0621449691540855</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>0.0787746921634775</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>0.0849472274353484</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>0.154486790670343</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>0.0447452878654551</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>0.0621035722000656</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>0.0637082262388039</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>0.0870316320768309</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>0.0148935139910483</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>0.0150302757057933</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>0.0264680497246913</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>0.0177456459318475</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8223,540 +6852,84 @@
               <c:f>master_cultures!$AO$2:$AO$188</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="187"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>5.69</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.5</c:v>
+                  <c:v>9.73</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.7</c:v>
+                  <c:v>9.39</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.8</c:v>
+                  <c:v>8.01</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.8</c:v>
+                  <c:v>11.78</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.4</c:v>
+                  <c:v>13.26</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.6</c:v>
+                  <c:v>8.94</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.9</c:v>
+                  <c:v>7.15</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.8</c:v>
+                  <c:v>9.73</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.1</c:v>
+                  <c:v>6.42</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.1</c:v>
+                  <c:v>2.76</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.2</c:v>
+                  <c:v>9.09</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.7</c:v>
+                  <c:v>14.97</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.2</c:v>
+                  <c:v>11.78</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>7.22</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>17.2</c:v>
+                  <c:v>11.09</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>12.5</c:v>
+                  <c:v>12.68</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>12.1</c:v>
+                  <c:v>8.01</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>7.1</c:v>
+                  <c:v>9.73</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.9</c:v>
+                  <c:v>8.8</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2.3</c:v>
+                  <c:v>15.75</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>35.3</c:v>
+                  <c:v>12.84</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>21.4</c:v>
+                  <c:v>8.96</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>21.7</c:v>
+                  <c:v>11.78</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>14.5</c:v>
+                  <c:v>10.81</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>3.7</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>19.8</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>11.3</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>5.8</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>5.7</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>9.5</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1.38854964080314</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>6.22977037438213</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1.01574465748398</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>2.4007666386282</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>3.2070200763168</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>9.53491237332075</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>2.63231105867986</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>9.89834421653803</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.311164035699694</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1.29155650315485</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>4.28892587494397</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>7.86073630741743</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>12.5536085085512</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>11.6742320225314</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>17.7310886608243</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>11.9750907790281</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>1.45360610411551</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>10.3353490711655</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>8.0193165204347</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>9.61727166716602</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>16.4753277156183</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>18.0441974139864</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.206227154911585</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>3.78584670100164</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.894983202203262</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.01</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.25</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.14</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.14</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.32</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0.38</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0.38</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>4.28</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>4.26</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>4.76</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>4.37</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>3.56</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>3.49</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>1.71</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>1.71</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>2.15</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>2.54</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>1.45</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>1.25</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>1.5</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>1.58</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>1.32</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>0.96</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>1.83</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>4.99</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>4.19</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>4.3</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>4.16</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>4.26</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>3.14</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>3.48</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>3.06</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>2.69</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>2.26</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>2.22</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>1.94</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>0.073684211</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>0.084210526</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>0.085106383</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>0.01</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>0.08</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>0.04</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>5.5</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>0.0695364238410596</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>7.6</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>5.1</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>5.1</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>1.1</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>1.2</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>0.4</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>1.5</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>5.69</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>9.73</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>9.39</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>8.01</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>11.78</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>13.26</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>8.94</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>7.15</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>9.73</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>6.42</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>2.76</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>9.09</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>14.97</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>11.78</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>7.22</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>11.09</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>12.68</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>8.01</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>9.73</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>8.8</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>15.75</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>12.84</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>8.96</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>11.78</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>10.81</c:v>
-                </c:pt>
-                <c:pt idx="152">
                   <c:v>16.08</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>2.4</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>2.9</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>3.3</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>3.2</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>3.2</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>4.3</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>2.9</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>2.9</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>4.6</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>2.2</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>3.2</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>4.2</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>0.0716534139217858</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>0.0593152981941857</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>0.0460937838894981</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>0.0126624164484942</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>0.0269325610224898</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>0.0238143841267373</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>0.0327481370330143</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>0.0323209839061975</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>0.0324967148172429</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>0.0394549225742002</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>0.0400965513427551</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>0.0404649548978106</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>0.0395471301091693</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>0.0886431015284976</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>0.020957003605465</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>0.0308621207053304</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>0.0443612245348016</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>0.0428271874079479</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>0.0127799295134205</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>0.00830115176078639</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>0.00928547359116495</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>0.00841077720521622</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8819,567 +6992,84 @@
               <c:f>master_cultures!$AP$2:$AP$188</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="187"/>
+                <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>6.39</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14</c:v>
+                  <c:v>8.13</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14</c:v>
+                  <c:v>4.53</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>29</c:v>
+                  <c:v>3.34</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19</c:v>
+                  <c:v>4.64</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.6</c:v>
+                  <c:v>10.34</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.1</c:v>
+                  <c:v>4.93</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.7</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.1</c:v>
+                  <c:v>4.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.8</c:v>
+                  <c:v>1.45</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.9</c:v>
+                  <c:v>5.59</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.3</c:v>
+                  <c:v>5.13</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.2</c:v>
+                  <c:v>3.34</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.5</c:v>
+                  <c:v>1.91</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>22</c:v>
+                  <c:v>4.31</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>49.1</c:v>
+                  <c:v>9.55</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>47.1</c:v>
+                  <c:v>3.25</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>25</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>51</c:v>
+                  <c:v>3.01</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>59</c:v>
+                  <c:v>7.2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>13.3</c:v>
+                  <c:v>7.75</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>17.5</c:v>
+                  <c:v>1.97</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>23.9</c:v>
+                  <c:v>3.34</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>38.7</c:v>
+                  <c:v>1.98</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>30.4</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>24.3</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>40.9</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>38.9</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>35.7</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>9.28033746611459</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>12.8456888541221</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>10.0772007105904</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1.34691574227145</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>8.20805536108538</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1.09929708300875</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>8.84562794567547</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.886093421006641</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.0502496257963335</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.515838111871423</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>67.9684307748193</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>37.3193390485025</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.50322098997341</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>12.462341369751</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>14.5171495382647</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>11.9107409058</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>8.52350536654416</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>9.59443586354036</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>69.3488374272237</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>21.2734200502151</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>32.7299033907647</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>19.3213237470882</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>19.05277331908</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>19.3883281223896</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>12.8446284452577</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>45.1170017935372</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>57.301722590566</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>69</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>65</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>43.67</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>47.99</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>53.91</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>62.58</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>71.73</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>73.91</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>32.51</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>35.17</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>41.27</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>51.78</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>64.9</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>37.39</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>40.14</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>45.42</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>49.78</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>54.65</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>54.41</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>70.03</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>71.35</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>65.28</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>65.72</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>64.28</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>53.53</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>53.78</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>60.49</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>60.33</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>59.34</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>58.7</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>58.53</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>0.536842105</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>0.463157895</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>0.457446809</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>0.34</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>0.24</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>35.8</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>29.2</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>55.1</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>0.59271523178808</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>56</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>33</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>33.6</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>26.2</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>10.4</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>16.8</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>22.4</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>19.4</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>80.2</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>7.7</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>10.2</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>6.9</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>6.39</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>8.13</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>4.53</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>3.34</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>4.64</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>10.34</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>4.93</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>4.6</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>1.45</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>5.59</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>5.13</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>3.34</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>1.91</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>4.31</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>9.55</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>3.25</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>3.01</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>7.2</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>7.75</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>1.97</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>3.34</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>1.98</c:v>
-                </c:pt>
-                <c:pt idx="152">
                   <c:v>5.58</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>21.3</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>26.1</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>35.4</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>18.8</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>23.2</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>28.7</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>6.7</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>7.8</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>5.5</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>7.3</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>11.2</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>0.604613325377816</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>0.6306890688125</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>0.646853184616807</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>0.693758642691294</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>0.454031443867735</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>0.534842904411954</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>0.563224021312562</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>0.661357558508973</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>0.599388216966824</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>0.428238197467388</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>0.501219403861513</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>0.596275117453373</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>0.671876287742252</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>0.153446368557124</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>0.281868787062314</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>0.285259193446433</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>0.323836035743518</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>0.323895412656285</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>0.390847108242858</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>0.518682177492692</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>0.549092996365743</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>0.554988246525083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9442,477 +7132,18 @@
               <c:f>master_cultures!$AQ$2:$AQ$188</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="187"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>4.6</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1.3</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1.3</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>2.2</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>4.9</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1.6</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1.2</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.4</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.454352984706014</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.411697930453323</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.223304363839989</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.325365558261136</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.184160276743516</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.961989060332397</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.713858403197846</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.612670355733102</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.322246769939556</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>1.13566668558685</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>5.48865179539637</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.705535009611373</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.747002661298785</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1.2013556460048</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.733944700392879</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>1.18529342417239</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>1.46103224384799</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.480775973103059</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>1.47651038672734</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>2.33301887781494</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.647351192666829</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>1.69021658366129</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>1.79981704402652</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1.18793252997312</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.879579105586369</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>26.4104190822172</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>28.9621293737269</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>0.24</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>0.37</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>0.58</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>0.56</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>0.84</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>0.31</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>0.26</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>0.36</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>0.12</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>0.23</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>0.17</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>0.34</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>0.31</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>1.28</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>1.18</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>0.89</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>0.62</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>0.61</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>0.37</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>0.36</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>0.64</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>0.55</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>0.43</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>0.39</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>0.29</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>0.010526316</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>0.010526316</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>0.010638298</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>0.004</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>0.01</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>0.006</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>1.1</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>13.7</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>22.9</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>1.1</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>1.2</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>0.4</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>0.0790791940219373</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>0.110109770635775</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>0.117210880046558</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>0.165552707354349</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>0.00284852504287042</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>0.00557903172573946</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>0.00607931839123843</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>0.014895194497873</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>0.0107098128790818</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>0.00234334324517002</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>0.00396981152718629</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>0.00590792621067985</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>0.00770855127295782</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>0.161247075843126</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>0.0029954114404571</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>0.00911248441589158</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>0.011231516294797</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>0.0215303926528836</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>0.00226053992117042</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>0.00294973328276556</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>0.00260172179470324</c:v>
-                </c:pt>
+                <c:ptCount val="26"/>
               </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
         <c:gapWidth val="0"/>
         <c:overlap val="100"/>
-        <c:axId val="94873260"/>
-        <c:axId val="55336298"/>
+        <c:axId val="66019246"/>
+        <c:axId val="21491123"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="94873260"/>
+        <c:axId val="66019246"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9944,7 +7175,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55336298"/>
+        <c:crossAx val="21491123"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9952,7 +7183,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55336298"/>
+        <c:axId val="21491123"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9991,7 +7222,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94873260"/>
+        <c:crossAx val="66019246"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10043,7 +7274,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -10627,11 +7858,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="72305665"/>
-        <c:axId val="11311899"/>
+        <c:axId val="9862437"/>
+        <c:axId val="95542735"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="72305665"/>
+        <c:axId val="9862437"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10707,12 +7938,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11311899"/>
+        <c:crossAx val="95542735"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="11311899"/>
+        <c:axId val="95542735"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10788,7 +8019,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72305665"/>
+        <c:crossAx val="9862437"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -10840,7 +8071,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -11398,11 +8629,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="68646156"/>
-        <c:axId val="33057556"/>
+        <c:axId val="49922300"/>
+        <c:axId val="77966759"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="68646156"/>
+        <c:axId val="49922300"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11478,12 +8709,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33057556"/>
+        <c:crossAx val="77966759"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="33057556"/>
+        <c:axId val="77966759"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11559,7 +8790,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68646156"/>
+        <c:crossAx val="49922300"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -11622,9 +8853,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>475560</xdr:colOff>
+      <xdr:colOff>475200</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>87840</xdr:rowOff>
+      <xdr:rowOff>87480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -11633,7 +8864,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="7668720" cy="6265080"/>
+        <a:ext cx="7668360" cy="6264720"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -11661,9 +8892,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>468720</xdr:colOff>
+      <xdr:colOff>468360</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>75960</xdr:rowOff>
+      <xdr:rowOff>75600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -11672,7 +8903,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="7661880" cy="6253200"/>
+        <a:ext cx="7661520" cy="6252840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -11696,9 +8927,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>474480</xdr:colOff>
+      <xdr:colOff>474120</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>85320</xdr:rowOff>
+      <xdr:rowOff>84960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -11707,7 +8938,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="7667640" cy="6262560"/>
+        <a:ext cx="7667280" cy="6262200"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -11721,13 +8952,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" recordCount="188" createdVersion="3">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" recordCount="187" createdVersion="3">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:BW188" sheet="master_cultures"/>
   </cacheSource>
   <cacheFields count="75">
     <cacheField name="sampleName" numFmtId="0">
-      <sharedItems count="184">
+      <sharedItems count="183">
         <s v="Bale2019_001_Cultures_ThAOA_Ca_Nitrosotenuis uzonesis_P-GDGT_DH_37"/>
         <s v="Bale2019_002_Cultures_ThAOA_Ca_Nitrosotenuis uzonesis_P-GDGT_DH_46"/>
         <s v="Bale2019_003_Cultures_ThAOA_Ca_Nitrosotenuis uzonesis_P-GDGT_DH_50"/>
@@ -11795,7 +9026,6 @@
         <s v="Elling2015_Culture_SCM1_22"/>
         <s v="Elling2015_Culture_SCM1_25"/>
         <s v="Elling2015_Culture_SCM1_28"/>
-        <s v="Elling2015_Culture_SCM1_35"/>
         <s v="Elling2017_culture_marineAOA_1G_P-GDGT_Nitrosopumilus adriaticus NF5"/>
         <s v="Elling2017_culture_marineAOA_1G_P-GDGT_Nitrosopumilus maritimus SCM1"/>
         <s v="Elling2017_culture_marineAOA_1G_P-GDGT_Nitrosopumilus piranensis D3C"/>
@@ -12259,7 +9489,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="sampleID_new" numFmtId="0">
-      <sharedItems count="188">
+      <sharedItems count="187">
         <s v="RR_culture_001"/>
         <s v="RR_culture_002"/>
         <s v="RR_culture_003"/>
@@ -12447,7 +9677,6 @@
         <s v="RR_culture_185"/>
         <s v="RR_culture_186"/>
         <s v="RR_culture_187"/>
-        <s v="RR_culture_188"/>
       </sharedItems>
     </cacheField>
     <cacheField name="reported_Temp" numFmtId="0">
@@ -15035,7 +12264,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="188">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="187">
   <r>
     <x v="0"/>
     <x v="22"/>
@@ -17425,83 +14654,6 @@
   </r>
   <r>
     <x v="67"/>
-    <x v="28"/>
-    <x v="24"/>
-    <x v="8"/>
-    <x v="2"/>
-    <x v="1"/>
-    <x v="1"/>
-    <x v="4"/>
-    <x v="9"/>
-    <x v="6"/>
-    <x v="1"/>
-    <x v="3"/>
-    <x v="7"/>
-    <x v="7"/>
-    <x v="9"/>
-    <x v="6"/>
-    <x v="1"/>
-    <x v="2"/>
-    <x v="2"/>
-    <x v="1"/>
-    <x v="1"/>
-    <x v="8"/>
-    <x v="31"/>
-    <x v="14"/>
-    <x v="0"/>
-    <x v="18"/>
-    <x v="7"/>
-    <x v="2"/>
-    <x v="9"/>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="4"/>
-    <x v="2"/>
-    <x v="11"/>
-    <x v="3"/>
-    <x v="6"/>
-    <x v="80"/>
-    <x v="70"/>
-    <x v="79"/>
-    <x v="95"/>
-    <x v="80"/>
-    <x v="169"/>
-    <x v="65"/>
-    <x v="113"/>
-    <x v="36"/>
-    <x v="26"/>
-    <x v="3"/>
-    <x v="5"/>
-    <x v="14"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="33"/>
-    <x v="42"/>
-    <x v="68"/>
-    <x v="52"/>
-    <x v="150"/>
-    <x v="55"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="1"/>
-    <x v="2"/>
-    <x v="4"/>
-    <x v="2"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="68"/>
     <x v="25"/>
     <x v="21"/>
     <x v="4"/>
@@ -17523,7 +14675,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="32"/>
+    <x v="31"/>
     <x v="11"/>
     <x v="0"/>
     <x v="17"/>
@@ -17578,7 +14730,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="69"/>
+    <x v="68"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -17600,7 +14752,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="33"/>
+    <x v="32"/>
     <x v="9"/>
     <x v="0"/>
     <x v="18"/>
@@ -17655,7 +14807,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="70"/>
+    <x v="69"/>
     <x v="8"/>
     <x v="26"/>
     <x v="10"/>
@@ -17677,7 +14829,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="34"/>
+    <x v="33"/>
     <x v="11"/>
     <x v="0"/>
     <x v="17"/>
@@ -17732,7 +14884,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="71"/>
+    <x v="70"/>
     <x v="23"/>
     <x v="8"/>
     <x v="6"/>
@@ -17754,7 +14906,7 @@
     <x v="0"/>
     <x v="9"/>
     <x v="5"/>
-    <x v="35"/>
+    <x v="34"/>
     <x v="9"/>
     <x v="0"/>
     <x v="18"/>
@@ -17809,7 +14961,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="72"/>
+    <x v="71"/>
     <x v="24"/>
     <x v="9"/>
     <x v="9"/>
@@ -17831,7 +14983,7 @@
     <x v="0"/>
     <x v="9"/>
     <x v="5"/>
-    <x v="36"/>
+    <x v="35"/>
     <x v="9"/>
     <x v="0"/>
     <x v="18"/>
@@ -17886,7 +15038,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="73"/>
+    <x v="72"/>
     <x v="25"/>
     <x v="21"/>
     <x v="4"/>
@@ -17908,7 +15060,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="37"/>
+    <x v="36"/>
     <x v="11"/>
     <x v="0"/>
     <x v="17"/>
@@ -17963,7 +15115,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="74"/>
+    <x v="73"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -17985,7 +15137,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="38"/>
+    <x v="37"/>
     <x v="9"/>
     <x v="0"/>
     <x v="18"/>
@@ -18040,7 +15192,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="75"/>
+    <x v="74"/>
     <x v="8"/>
     <x v="26"/>
     <x v="10"/>
@@ -18062,7 +15214,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="39"/>
+    <x v="38"/>
     <x v="11"/>
     <x v="0"/>
     <x v="17"/>
@@ -18117,7 +15269,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="76"/>
+    <x v="75"/>
     <x v="23"/>
     <x v="8"/>
     <x v="6"/>
@@ -18139,7 +15291,7 @@
     <x v="0"/>
     <x v="9"/>
     <x v="5"/>
-    <x v="40"/>
+    <x v="39"/>
     <x v="9"/>
     <x v="0"/>
     <x v="18"/>
@@ -18194,7 +15346,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="77"/>
+    <x v="76"/>
     <x v="24"/>
     <x v="9"/>
     <x v="9"/>
@@ -18216,7 +15368,7 @@
     <x v="0"/>
     <x v="9"/>
     <x v="5"/>
-    <x v="41"/>
+    <x v="40"/>
     <x v="9"/>
     <x v="0"/>
     <x v="18"/>
@@ -18271,7 +15423,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="88"/>
+    <x v="87"/>
     <x v="17"/>
     <x v="5"/>
     <x v="28"/>
@@ -18293,7 +15445,7 @@
     <x v="0"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="42"/>
+    <x v="41"/>
     <x v="25"/>
     <x v="0"/>
     <x v="15"/>
@@ -18348,7 +15500,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="89"/>
+    <x v="88"/>
     <x v="14"/>
     <x v="10"/>
     <x v="18"/>
@@ -18370,7 +15522,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="43"/>
+    <x v="42"/>
     <x v="17"/>
     <x v="0"/>
     <x v="20"/>
@@ -18425,7 +15577,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="90"/>
+    <x v="89"/>
     <x v="14"/>
     <x v="10"/>
     <x v="18"/>
@@ -18447,7 +15599,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="44"/>
+    <x v="43"/>
     <x v="17"/>
     <x v="0"/>
     <x v="20"/>
@@ -18502,7 +15654,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="78"/>
+    <x v="77"/>
     <x v="25"/>
     <x v="21"/>
     <x v="4"/>
@@ -18524,7 +15676,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="45"/>
+    <x v="44"/>
     <x v="11"/>
     <x v="0"/>
     <x v="17"/>
@@ -18579,7 +15731,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="79"/>
+    <x v="78"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -18601,7 +15753,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="46"/>
+    <x v="45"/>
     <x v="9"/>
     <x v="0"/>
     <x v="18"/>
@@ -18656,7 +15808,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="80"/>
+    <x v="79"/>
     <x v="8"/>
     <x v="26"/>
     <x v="10"/>
@@ -18678,7 +15830,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="47"/>
+    <x v="46"/>
     <x v="11"/>
     <x v="0"/>
     <x v="17"/>
@@ -18733,7 +15885,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="81"/>
+    <x v="80"/>
     <x v="23"/>
     <x v="8"/>
     <x v="6"/>
@@ -18755,7 +15907,7 @@
     <x v="0"/>
     <x v="9"/>
     <x v="5"/>
-    <x v="48"/>
+    <x v="47"/>
     <x v="9"/>
     <x v="0"/>
     <x v="18"/>
@@ -18810,7 +15962,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="82"/>
+    <x v="81"/>
     <x v="24"/>
     <x v="9"/>
     <x v="9"/>
@@ -18832,7 +15984,7 @@
     <x v="0"/>
     <x v="9"/>
     <x v="5"/>
-    <x v="49"/>
+    <x v="48"/>
     <x v="9"/>
     <x v="0"/>
     <x v="18"/>
@@ -18887,7 +16039,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="91"/>
+    <x v="90"/>
     <x v="14"/>
     <x v="10"/>
     <x v="18"/>
@@ -18909,7 +16061,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="50"/>
+    <x v="49"/>
     <x v="17"/>
     <x v="0"/>
     <x v="20"/>
@@ -18964,7 +16116,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="83"/>
+    <x v="82"/>
     <x v="25"/>
     <x v="21"/>
     <x v="4"/>
@@ -18986,7 +16138,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="51"/>
+    <x v="50"/>
     <x v="11"/>
     <x v="0"/>
     <x v="17"/>
@@ -19041,7 +16193,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="84"/>
+    <x v="83"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -19063,7 +16215,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="52"/>
+    <x v="51"/>
     <x v="9"/>
     <x v="0"/>
     <x v="18"/>
@@ -19118,7 +16270,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="85"/>
+    <x v="84"/>
     <x v="8"/>
     <x v="26"/>
     <x v="10"/>
@@ -19140,7 +16292,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="53"/>
+    <x v="52"/>
     <x v="11"/>
     <x v="0"/>
     <x v="17"/>
@@ -19195,7 +16347,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="86"/>
+    <x v="85"/>
     <x v="23"/>
     <x v="8"/>
     <x v="6"/>
@@ -19217,7 +16369,7 @@
     <x v="0"/>
     <x v="9"/>
     <x v="5"/>
-    <x v="54"/>
+    <x v="53"/>
     <x v="9"/>
     <x v="0"/>
     <x v="18"/>
@@ -19272,7 +16424,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="87"/>
+    <x v="86"/>
     <x v="24"/>
     <x v="13"/>
     <x v="9"/>
@@ -19294,7 +16446,7 @@
     <x v="0"/>
     <x v="9"/>
     <x v="5"/>
-    <x v="55"/>
+    <x v="54"/>
     <x v="9"/>
     <x v="0"/>
     <x v="18"/>
@@ -19349,7 +16501,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="92"/>
+    <x v="91"/>
     <x v="17"/>
     <x v="5"/>
     <x v="28"/>
@@ -19371,7 +16523,7 @@
     <x v="0"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="56"/>
+    <x v="55"/>
     <x v="25"/>
     <x v="0"/>
     <x v="15"/>
@@ -19426,7 +16578,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="93"/>
+    <x v="92"/>
     <x v="14"/>
     <x v="10"/>
     <x v="18"/>
@@ -19448,7 +16600,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="57"/>
+    <x v="56"/>
     <x v="14"/>
     <x v="0"/>
     <x v="20"/>
@@ -19503,7 +16655,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="94"/>
+    <x v="93"/>
     <x v="14"/>
     <x v="10"/>
     <x v="18"/>
@@ -19525,7 +16677,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="58"/>
+    <x v="57"/>
     <x v="17"/>
     <x v="0"/>
     <x v="20"/>
@@ -19580,28 +16732,105 @@
     <x v="0"/>
   </r>
   <r>
+    <x v="122"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="28"/>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="58"/>
+    <x v="28"/>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="9"/>
+    <x v="3"/>
+    <x v="10"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="11"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="28"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="17"/>
+    <x v="0"/>
+    <x v="26"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="163"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="10"/>
+    <x v="1"/>
+    <x v="10"/>
+    <x v="0"/>
+  </r>
+  <r>
     <x v="123"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="28"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="24"/>
     <x v="2"/>
     <x v="4"/>
     <x v="2"/>
     <x v="1"/>
     <x v="2"/>
-    <x v="3"/>
+    <x v="9"/>
     <x v="2"/>
     <x v="5"/>
     <x v="3"/>
     <x v="3"/>
     <x v="2"/>
-    <x v="3"/>
+    <x v="9"/>
     <x v="5"/>
     <x v="0"/>
     <x v="0"/>
     <x v="1"/>
-    <x v="2"/>
-    <x v="1"/>
+    <x v="8"/>
+    <x v="2"/>
     <x v="59"/>
     <x v="28"/>
     <x v="0"/>
@@ -19617,25 +16846,25 @@
     <x v="3"/>
     <x v="2"/>
     <x v="3"/>
-    <x v="28"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="17"/>
-    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="11"/>
+    <x v="13"/>
     <x v="26"/>
     <x v="3"/>
-    <x v="4"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="163"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="167"/>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
@@ -19647,9 +16876,9 @@
     <x v="0"/>
     <x v="0"/>
     <x v="1"/>
-    <x v="1"/>
-    <x v="1"/>
-    <x v="0"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
     <x v="0"/>
     <x v="10"/>
     <x v="1"/>
@@ -19658,83 +16887,6 @@
   </r>
   <r>
     <x v="124"/>
-    <x v="1"/>
-    <x v="1"/>
-    <x v="24"/>
-    <x v="2"/>
-    <x v="4"/>
-    <x v="2"/>
-    <x v="1"/>
-    <x v="2"/>
-    <x v="9"/>
-    <x v="2"/>
-    <x v="5"/>
-    <x v="3"/>
-    <x v="3"/>
-    <x v="2"/>
-    <x v="9"/>
-    <x v="5"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="8"/>
-    <x v="2"/>
-    <x v="60"/>
-    <x v="28"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="7"/>
-    <x v="2"/>
-    <x v="9"/>
-    <x v="3"/>
-    <x v="10"/>
-    <x v="4"/>
-    <x v="2"/>
-    <x v="11"/>
-    <x v="3"/>
-    <x v="2"/>
-    <x v="3"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="4"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="11"/>
-    <x v="13"/>
-    <x v="26"/>
-    <x v="3"/>
-    <x v="3"/>
-    <x v="2"/>
-    <x v="1"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="167"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="10"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="2"/>
-    <x v="1"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="10"/>
-    <x v="1"/>
-    <x v="10"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="125"/>
     <x v="11"/>
     <x v="17"/>
     <x v="21"/>
@@ -19756,7 +16908,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="61"/>
+    <x v="60"/>
     <x v="26"/>
     <x v="0"/>
     <x v="8"/>
@@ -19811,7 +16963,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="126"/>
+    <x v="125"/>
     <x v="26"/>
     <x v="31"/>
     <x v="22"/>
@@ -19833,7 +16985,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="62"/>
+    <x v="61"/>
     <x v="29"/>
     <x v="0"/>
     <x v="8"/>
@@ -19888,7 +17040,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="127"/>
+    <x v="126"/>
     <x v="2"/>
     <x v="33"/>
     <x v="26"/>
@@ -19910,7 +17062,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="63"/>
+    <x v="62"/>
     <x v="29"/>
     <x v="0"/>
     <x v="8"/>
@@ -19965,7 +17117,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="130"/>
+    <x v="129"/>
     <x v="10"/>
     <x v="32"/>
     <x v="25"/>
@@ -19987,7 +17139,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="64"/>
+    <x v="63"/>
     <x v="29"/>
     <x v="0"/>
     <x v="10"/>
@@ -20042,7 +17194,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="128"/>
+    <x v="127"/>
     <x v="9"/>
     <x v="15"/>
     <x v="23"/>
@@ -20064,7 +17216,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="65"/>
+    <x v="64"/>
     <x v="29"/>
     <x v="0"/>
     <x v="11"/>
@@ -20119,7 +17271,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="129"/>
+    <x v="128"/>
     <x v="32"/>
     <x v="16"/>
     <x v="23"/>
@@ -20141,7 +17293,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="66"/>
+    <x v="65"/>
     <x v="29"/>
     <x v="0"/>
     <x v="12"/>
@@ -20196,7 +17348,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="131"/>
+    <x v="130"/>
     <x v="14"/>
     <x v="10"/>
     <x v="18"/>
@@ -20218,7 +17370,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="67"/>
+    <x v="66"/>
     <x v="17"/>
     <x v="0"/>
     <x v="20"/>
@@ -20273,7 +17425,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="132"/>
+    <x v="131"/>
     <x v="14"/>
     <x v="10"/>
     <x v="18"/>
@@ -20295,7 +17447,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="68"/>
+    <x v="67"/>
     <x v="16"/>
     <x v="0"/>
     <x v="20"/>
@@ -20350,7 +17502,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="133"/>
+    <x v="132"/>
     <x v="14"/>
     <x v="10"/>
     <x v="18"/>
@@ -20372,7 +17524,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="69"/>
+    <x v="68"/>
     <x v="19"/>
     <x v="0"/>
     <x v="20"/>
@@ -20427,7 +17579,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="134"/>
+    <x v="133"/>
     <x v="14"/>
     <x v="10"/>
     <x v="18"/>
@@ -20449,7 +17601,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="70"/>
+    <x v="69"/>
     <x v="17"/>
     <x v="0"/>
     <x v="20"/>
@@ -20504,7 +17656,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="138"/>
+    <x v="137"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -20526,7 +17678,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="71"/>
+    <x v="70"/>
     <x v="1"/>
     <x v="0"/>
     <x v="22"/>
@@ -20581,7 +17733,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="139"/>
+    <x v="138"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -20603,7 +17755,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="72"/>
+    <x v="71"/>
     <x v="4"/>
     <x v="0"/>
     <x v="22"/>
@@ -20658,7 +17810,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="140"/>
+    <x v="139"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -20680,7 +17832,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="73"/>
+    <x v="72"/>
     <x v="7"/>
     <x v="0"/>
     <x v="22"/>
@@ -20735,7 +17887,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="141"/>
+    <x v="140"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -20757,7 +17909,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="74"/>
+    <x v="73"/>
     <x v="11"/>
     <x v="0"/>
     <x v="22"/>
@@ -20812,7 +17964,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="142"/>
+    <x v="141"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -20834,7 +17986,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="75"/>
+    <x v="74"/>
     <x v="13"/>
     <x v="0"/>
     <x v="22"/>
@@ -20889,7 +18041,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="143"/>
+    <x v="142"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -20911,7 +18063,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="76"/>
+    <x v="75"/>
     <x v="14"/>
     <x v="0"/>
     <x v="22"/>
@@ -20966,7 +18118,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="144"/>
+    <x v="143"/>
     <x v="15"/>
     <x v="22"/>
     <x v="1"/>
@@ -20988,7 +18140,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="77"/>
+    <x v="76"/>
     <x v="0"/>
     <x v="0"/>
     <x v="22"/>
@@ -21043,7 +18195,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="145"/>
+    <x v="144"/>
     <x v="15"/>
     <x v="22"/>
     <x v="1"/>
@@ -21065,7 +18217,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="78"/>
+    <x v="77"/>
     <x v="1"/>
     <x v="0"/>
     <x v="22"/>
@@ -21120,7 +18272,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="146"/>
+    <x v="145"/>
     <x v="15"/>
     <x v="22"/>
     <x v="1"/>
@@ -21142,7 +18294,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="79"/>
+    <x v="78"/>
     <x v="4"/>
     <x v="0"/>
     <x v="22"/>
@@ -21197,7 +18349,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="147"/>
+    <x v="146"/>
     <x v="15"/>
     <x v="22"/>
     <x v="1"/>
@@ -21219,7 +18371,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="80"/>
+    <x v="79"/>
     <x v="7"/>
     <x v="0"/>
     <x v="22"/>
@@ -21274,7 +18426,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="148"/>
+    <x v="147"/>
     <x v="15"/>
     <x v="22"/>
     <x v="1"/>
@@ -21296,7 +18448,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="81"/>
+    <x v="80"/>
     <x v="11"/>
     <x v="0"/>
     <x v="22"/>
@@ -21351,7 +18503,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="149"/>
+    <x v="148"/>
     <x v="16"/>
     <x v="25"/>
     <x v="0"/>
@@ -21373,7 +18525,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="82"/>
+    <x v="81"/>
     <x v="0"/>
     <x v="0"/>
     <x v="22"/>
@@ -21428,7 +18580,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="150"/>
+    <x v="149"/>
     <x v="16"/>
     <x v="25"/>
     <x v="0"/>
@@ -21450,7 +18602,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="83"/>
+    <x v="82"/>
     <x v="1"/>
     <x v="0"/>
     <x v="22"/>
@@ -21505,7 +18657,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="151"/>
+    <x v="150"/>
     <x v="16"/>
     <x v="25"/>
     <x v="0"/>
@@ -21527,7 +18679,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="84"/>
+    <x v="83"/>
     <x v="4"/>
     <x v="0"/>
     <x v="22"/>
@@ -21582,7 +18734,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="152"/>
+    <x v="151"/>
     <x v="16"/>
     <x v="25"/>
     <x v="0"/>
@@ -21604,7 +18756,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="85"/>
+    <x v="84"/>
     <x v="5"/>
     <x v="0"/>
     <x v="22"/>
@@ -21659,7 +18811,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="153"/>
+    <x v="152"/>
     <x v="16"/>
     <x v="25"/>
     <x v="0"/>
@@ -21681,7 +18833,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="86"/>
+    <x v="85"/>
     <x v="7"/>
     <x v="0"/>
     <x v="22"/>
@@ -21736,7 +18888,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="154"/>
+    <x v="153"/>
     <x v="27"/>
     <x v="28"/>
     <x v="3"/>
@@ -21758,7 +18910,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="8"/>
-    <x v="87"/>
+    <x v="86"/>
     <x v="7"/>
     <x v="0"/>
     <x v="22"/>
@@ -21813,7 +18965,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="155"/>
+    <x v="154"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -21835,7 +18987,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="88"/>
+    <x v="87"/>
     <x v="11"/>
     <x v="0"/>
     <x v="22"/>
@@ -21890,7 +19042,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="156"/>
+    <x v="155"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -21912,7 +19064,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="89"/>
+    <x v="88"/>
     <x v="11"/>
     <x v="0"/>
     <x v="22"/>
@@ -21967,7 +19119,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="157"/>
+    <x v="156"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -21989,7 +19141,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="90"/>
+    <x v="89"/>
     <x v="11"/>
     <x v="0"/>
     <x v="22"/>
@@ -22044,7 +19196,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="158"/>
+    <x v="157"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -22066,7 +19218,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="91"/>
+    <x v="90"/>
     <x v="11"/>
     <x v="0"/>
     <x v="22"/>
@@ -22121,7 +19273,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="159"/>
+    <x v="158"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -22143,7 +19295,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="92"/>
+    <x v="91"/>
     <x v="11"/>
     <x v="0"/>
     <x v="22"/>
@@ -22198,7 +19350,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="160"/>
+    <x v="159"/>
     <x v="27"/>
     <x v="28"/>
     <x v="3"/>
@@ -22220,7 +19372,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="8"/>
-    <x v="93"/>
+    <x v="92"/>
     <x v="8"/>
     <x v="0"/>
     <x v="22"/>
@@ -22275,7 +19427,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="161"/>
+    <x v="160"/>
     <x v="27"/>
     <x v="28"/>
     <x v="3"/>
@@ -22297,7 +19449,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="8"/>
-    <x v="94"/>
+    <x v="93"/>
     <x v="8"/>
     <x v="0"/>
     <x v="22"/>
@@ -22352,7 +19504,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="162"/>
+    <x v="161"/>
     <x v="27"/>
     <x v="28"/>
     <x v="3"/>
@@ -22374,7 +19526,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="8"/>
-    <x v="95"/>
+    <x v="94"/>
     <x v="8"/>
     <x v="0"/>
     <x v="22"/>
@@ -22429,7 +19581,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="163"/>
+    <x v="162"/>
     <x v="27"/>
     <x v="28"/>
     <x v="3"/>
@@ -22451,7 +19603,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="8"/>
-    <x v="96"/>
+    <x v="95"/>
     <x v="8"/>
     <x v="0"/>
     <x v="22"/>
@@ -22506,7 +19658,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="164"/>
+    <x v="163"/>
     <x v="27"/>
     <x v="28"/>
     <x v="3"/>
@@ -22528,7 +19680,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="8"/>
-    <x v="97"/>
+    <x v="96"/>
     <x v="8"/>
     <x v="0"/>
     <x v="22"/>
@@ -22583,7 +19735,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="165"/>
+    <x v="164"/>
     <x v="27"/>
     <x v="28"/>
     <x v="3"/>
@@ -22605,7 +19757,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="8"/>
-    <x v="98"/>
+    <x v="97"/>
     <x v="8"/>
     <x v="0"/>
     <x v="22"/>
@@ -22660,7 +19812,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="166"/>
+    <x v="165"/>
     <x v="27"/>
     <x v="28"/>
     <x v="3"/>
@@ -22682,7 +19834,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="8"/>
-    <x v="99"/>
+    <x v="98"/>
     <x v="8"/>
     <x v="0"/>
     <x v="22"/>
@@ -22737,7 +19889,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="119"/>
+    <x v="118"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -22759,7 +19911,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="100"/>
+    <x v="99"/>
     <x v="9"/>
     <x v="0"/>
     <x v="19"/>
@@ -22814,7 +19966,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="118"/>
+    <x v="117"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -22836,7 +19988,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="101"/>
+    <x v="100"/>
     <x v="9"/>
     <x v="0"/>
     <x v="19"/>
@@ -22891,7 +20043,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="117"/>
+    <x v="116"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -22913,7 +20065,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="102"/>
+    <x v="101"/>
     <x v="9"/>
     <x v="0"/>
     <x v="19"/>
@@ -22968,7 +20120,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="136"/>
+    <x v="135"/>
     <x v="29"/>
     <x v="4"/>
     <x v="13"/>
@@ -22990,7 +20142,7 @@
     <x v="1"/>
     <x v="7"/>
     <x v="4"/>
-    <x v="103"/>
+    <x v="102"/>
     <x v="5"/>
     <x v="0"/>
     <x v="16"/>
@@ -23045,7 +20197,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="137"/>
+    <x v="136"/>
     <x v="30"/>
     <x v="27"/>
     <x v="11"/>
@@ -23067,7 +20219,7 @@
     <x v="1"/>
     <x v="3"/>
     <x v="6"/>
-    <x v="104"/>
+    <x v="103"/>
     <x v="7"/>
     <x v="0"/>
     <x v="21"/>
@@ -23122,7 +20274,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="135"/>
+    <x v="134"/>
     <x v="5"/>
     <x v="23"/>
     <x v="7"/>
@@ -23144,7 +20296,7 @@
     <x v="1"/>
     <x v="4"/>
     <x v="7"/>
-    <x v="105"/>
+    <x v="104"/>
     <x v="7"/>
     <x v="0"/>
     <x v="21"/>
@@ -23199,7 +20351,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="168"/>
+    <x v="167"/>
     <x v="19"/>
     <x v="19"/>
     <x v="12"/>
@@ -23221,7 +20373,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="106"/>
+    <x v="105"/>
     <x v="7"/>
     <x v="0"/>
     <x v="14"/>
@@ -23276,7 +20428,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="169"/>
+    <x v="168"/>
     <x v="18"/>
     <x v="3"/>
     <x v="28"/>
@@ -23298,7 +20450,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="107"/>
+    <x v="106"/>
     <x v="15"/>
     <x v="0"/>
     <x v="18"/>
@@ -23353,7 +20505,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="170"/>
+    <x v="169"/>
     <x v="13"/>
     <x v="29"/>
     <x v="19"/>
@@ -23375,7 +20527,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="108"/>
+    <x v="107"/>
     <x v="15"/>
     <x v="0"/>
     <x v="16"/>
@@ -23430,7 +20582,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="167"/>
+    <x v="166"/>
     <x v="28"/>
     <x v="24"/>
     <x v="8"/>
@@ -23452,7 +20604,7 @@
     <x v="1"/>
     <x v="1"/>
     <x v="8"/>
-    <x v="109"/>
+    <x v="108"/>
     <x v="9"/>
     <x v="0"/>
     <x v="16"/>
@@ -23507,7 +20659,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="171"/>
+    <x v="170"/>
     <x v="4"/>
     <x v="14"/>
     <x v="14"/>
@@ -23529,7 +20681,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="110"/>
+    <x v="109"/>
     <x v="0"/>
     <x v="0"/>
     <x v="22"/>
@@ -23584,7 +20736,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="120"/>
+    <x v="119"/>
     <x v="19"/>
     <x v="19"/>
     <x v="12"/>
@@ -23606,7 +20758,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="111"/>
+    <x v="110"/>
     <x v="7"/>
     <x v="0"/>
     <x v="14"/>
@@ -23661,7 +20813,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="121"/>
+    <x v="120"/>
     <x v="20"/>
     <x v="11"/>
     <x v="17"/>
@@ -23683,7 +20835,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="112"/>
+    <x v="111"/>
     <x v="7"/>
     <x v="0"/>
     <x v="22"/>
@@ -23738,7 +20890,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="122"/>
+    <x v="121"/>
     <x v="21"/>
     <x v="6"/>
     <x v="20"/>
@@ -23760,7 +20912,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="113"/>
+    <x v="112"/>
     <x v="11"/>
     <x v="0"/>
     <x v="13"/>
@@ -23837,7 +20989,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="9"/>
-    <x v="114"/>
+    <x v="113"/>
     <x v="23"/>
     <x v="0"/>
     <x v="5"/>
@@ -23914,7 +21066,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="9"/>
-    <x v="115"/>
+    <x v="114"/>
     <x v="24"/>
     <x v="0"/>
     <x v="5"/>
@@ -23991,7 +21143,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="9"/>
-    <x v="116"/>
+    <x v="115"/>
     <x v="26"/>
     <x v="0"/>
     <x v="5"/>
@@ -24068,7 +21220,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="9"/>
-    <x v="117"/>
+    <x v="116"/>
     <x v="27"/>
     <x v="0"/>
     <x v="5"/>
@@ -24145,7 +21297,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="9"/>
-    <x v="118"/>
+    <x v="117"/>
     <x v="27"/>
     <x v="0"/>
     <x v="6"/>
@@ -24222,7 +21374,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="9"/>
-    <x v="119"/>
+    <x v="118"/>
     <x v="27"/>
     <x v="0"/>
     <x v="7"/>
@@ -24299,7 +21451,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="9"/>
-    <x v="120"/>
+    <x v="119"/>
     <x v="27"/>
     <x v="0"/>
     <x v="8"/>
@@ -24376,7 +21528,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="9"/>
-    <x v="121"/>
+    <x v="120"/>
     <x v="27"/>
     <x v="0"/>
     <x v="9"/>
@@ -24453,7 +21605,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="9"/>
-    <x v="122"/>
+    <x v="121"/>
     <x v="27"/>
     <x v="0"/>
     <x v="5"/>
@@ -24530,7 +21682,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="9"/>
-    <x v="123"/>
+    <x v="122"/>
     <x v="27"/>
     <x v="0"/>
     <x v="5"/>
@@ -24607,7 +21759,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="9"/>
-    <x v="124"/>
+    <x v="123"/>
     <x v="27"/>
     <x v="0"/>
     <x v="5"/>
@@ -24684,7 +21836,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="9"/>
-    <x v="125"/>
+    <x v="124"/>
     <x v="27"/>
     <x v="0"/>
     <x v="5"/>
@@ -24761,7 +21913,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="9"/>
-    <x v="126"/>
+    <x v="125"/>
     <x v="27"/>
     <x v="0"/>
     <x v="5"/>
@@ -24838,7 +21990,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="9"/>
-    <x v="127"/>
+    <x v="126"/>
     <x v="27"/>
     <x v="0"/>
     <x v="5"/>
@@ -24893,7 +22045,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="95"/>
+    <x v="94"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -24915,7 +22067,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="128"/>
+    <x v="127"/>
     <x v="20"/>
     <x v="0"/>
     <x v="2"/>
@@ -24970,7 +22122,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="100"/>
+    <x v="99"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -24992,7 +22144,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="129"/>
+    <x v="128"/>
     <x v="21"/>
     <x v="0"/>
     <x v="2"/>
@@ -25047,7 +22199,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="105"/>
+    <x v="104"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -25069,7 +22221,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="130"/>
+    <x v="129"/>
     <x v="22"/>
     <x v="0"/>
     <x v="2"/>
@@ -25124,7 +22276,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="106"/>
+    <x v="105"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -25146,7 +22298,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="131"/>
+    <x v="130"/>
     <x v="20"/>
     <x v="0"/>
     <x v="2"/>
@@ -25201,7 +22353,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -25223,7 +22375,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="132"/>
+    <x v="131"/>
     <x v="21"/>
     <x v="0"/>
     <x v="2"/>
@@ -25278,7 +22430,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="116"/>
+    <x v="115"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -25300,7 +22452,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="133"/>
+    <x v="132"/>
     <x v="22"/>
     <x v="0"/>
     <x v="2"/>
@@ -25355,7 +22507,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="96"/>
+    <x v="95"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -25377,7 +22529,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="134"/>
+    <x v="133"/>
     <x v="21"/>
     <x v="0"/>
     <x v="0"/>
@@ -25432,7 +22584,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="97"/>
+    <x v="96"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -25454,7 +22606,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="135"/>
+    <x v="134"/>
     <x v="21"/>
     <x v="0"/>
     <x v="1"/>
@@ -25509,7 +22661,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="100"/>
+    <x v="99"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -25531,7 +22683,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="136"/>
+    <x v="135"/>
     <x v="21"/>
     <x v="0"/>
     <x v="2"/>
@@ -25586,7 +22738,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="103"/>
+    <x v="102"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -25608,7 +22760,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="137"/>
+    <x v="136"/>
     <x v="21"/>
     <x v="0"/>
     <x v="3"/>
@@ -25663,7 +22815,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="104"/>
+    <x v="103"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -25685,7 +22837,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="138"/>
+    <x v="137"/>
     <x v="21"/>
     <x v="0"/>
     <x v="4"/>
@@ -25740,7 +22892,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="107"/>
+    <x v="106"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -25762,7 +22914,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="139"/>
+    <x v="138"/>
     <x v="21"/>
     <x v="0"/>
     <x v="0"/>
@@ -25817,7 +22969,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="108"/>
+    <x v="107"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -25839,7 +22991,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="140"/>
+    <x v="139"/>
     <x v="21"/>
     <x v="0"/>
     <x v="1"/>
@@ -25894,7 +23046,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -25916,7 +23068,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="141"/>
+    <x v="140"/>
     <x v="21"/>
     <x v="0"/>
     <x v="2"/>
@@ -25971,7 +23123,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="114"/>
+    <x v="113"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -25993,7 +23145,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="142"/>
+    <x v="141"/>
     <x v="21"/>
     <x v="0"/>
     <x v="3"/>
@@ -26048,7 +23200,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="115"/>
+    <x v="114"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -26070,7 +23222,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="143"/>
+    <x v="142"/>
     <x v="21"/>
     <x v="0"/>
     <x v="4"/>
@@ -26125,7 +23277,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="101"/>
+    <x v="100"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -26147,7 +23299,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="144"/>
+    <x v="143"/>
     <x v="21"/>
     <x v="0"/>
     <x v="2"/>
@@ -26202,7 +23354,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="98"/>
+    <x v="97"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -26224,7 +23376,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="145"/>
+    <x v="144"/>
     <x v="21"/>
     <x v="0"/>
     <x v="2"/>
@@ -26279,7 +23431,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="100"/>
+    <x v="99"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -26301,7 +23453,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="146"/>
+    <x v="145"/>
     <x v="21"/>
     <x v="0"/>
     <x v="2"/>
@@ -26356,7 +23508,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="102"/>
+    <x v="101"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -26378,7 +23530,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="147"/>
+    <x v="146"/>
     <x v="21"/>
     <x v="0"/>
     <x v="2"/>
@@ -26433,7 +23585,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="99"/>
+    <x v="98"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -26455,7 +23607,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="148"/>
+    <x v="147"/>
     <x v="21"/>
     <x v="0"/>
     <x v="2"/>
@@ -26510,7 +23662,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="112"/>
+    <x v="111"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -26532,7 +23684,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="149"/>
+    <x v="148"/>
     <x v="21"/>
     <x v="0"/>
     <x v="2"/>
@@ -26587,7 +23739,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="109"/>
+    <x v="108"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -26609,7 +23761,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="150"/>
+    <x v="149"/>
     <x v="21"/>
     <x v="0"/>
     <x v="2"/>
@@ -26664,7 +23816,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="111"/>
+    <x v="110"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -26686,7 +23838,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="151"/>
+    <x v="150"/>
     <x v="21"/>
     <x v="0"/>
     <x v="2"/>
@@ -26741,7 +23893,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="113"/>
+    <x v="112"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -26763,7 +23915,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="152"/>
+    <x v="151"/>
     <x v="21"/>
     <x v="0"/>
     <x v="2"/>
@@ -26818,7 +23970,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="110"/>
+    <x v="109"/>
     <x v="12"/>
     <x v="30"/>
     <x v="27"/>
@@ -26840,7 +23992,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="153"/>
+    <x v="152"/>
     <x v="21"/>
     <x v="0"/>
     <x v="2"/>
@@ -26895,7 +24047,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="178"/>
+    <x v="177"/>
     <x v="8"/>
     <x v="26"/>
     <x v="10"/>
@@ -26917,7 +24069,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="154"/>
+    <x v="153"/>
     <x v="7"/>
     <x v="0"/>
     <x v="22"/>
@@ -26972,7 +24124,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="180"/>
+    <x v="179"/>
     <x v="8"/>
     <x v="26"/>
     <x v="10"/>
@@ -26994,7 +24146,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="155"/>
+    <x v="154"/>
     <x v="11"/>
     <x v="0"/>
     <x v="22"/>
@@ -27049,7 +24201,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="182"/>
+    <x v="181"/>
     <x v="8"/>
     <x v="26"/>
     <x v="10"/>
@@ -27071,7 +24223,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="156"/>
+    <x v="155"/>
     <x v="14"/>
     <x v="0"/>
     <x v="22"/>
@@ -27126,7 +24278,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="179"/>
+    <x v="178"/>
     <x v="8"/>
     <x v="26"/>
     <x v="10"/>
@@ -27148,7 +24300,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="157"/>
+    <x v="156"/>
     <x v="7"/>
     <x v="0"/>
     <x v="22"/>
@@ -27203,7 +24355,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="181"/>
+    <x v="180"/>
     <x v="8"/>
     <x v="26"/>
     <x v="10"/>
@@ -27225,7 +24377,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="158"/>
+    <x v="157"/>
     <x v="11"/>
     <x v="0"/>
     <x v="22"/>
@@ -27280,7 +24432,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="183"/>
+    <x v="182"/>
     <x v="8"/>
     <x v="26"/>
     <x v="10"/>
@@ -27302,7 +24454,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="159"/>
+    <x v="158"/>
     <x v="14"/>
     <x v="0"/>
     <x v="22"/>
@@ -27357,7 +24509,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="172"/>
+    <x v="171"/>
     <x v="25"/>
     <x v="21"/>
     <x v="4"/>
@@ -27379,7 +24531,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="160"/>
+    <x v="159"/>
     <x v="4"/>
     <x v="0"/>
     <x v="22"/>
@@ -27434,7 +24586,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="174"/>
+    <x v="173"/>
     <x v="25"/>
     <x v="21"/>
     <x v="4"/>
@@ -27456,7 +24608,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="161"/>
+    <x v="160"/>
     <x v="7"/>
     <x v="0"/>
     <x v="22"/>
@@ -27511,7 +24663,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="176"/>
+    <x v="175"/>
     <x v="25"/>
     <x v="21"/>
     <x v="4"/>
@@ -27533,7 +24685,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="162"/>
+    <x v="161"/>
     <x v="11"/>
     <x v="0"/>
     <x v="22"/>
@@ -27588,7 +24740,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="173"/>
+    <x v="172"/>
     <x v="25"/>
     <x v="21"/>
     <x v="4"/>
@@ -27610,7 +24762,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="163"/>
+    <x v="162"/>
     <x v="4"/>
     <x v="0"/>
     <x v="22"/>
@@ -27665,7 +24817,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="175"/>
+    <x v="174"/>
     <x v="25"/>
     <x v="21"/>
     <x v="4"/>
@@ -27687,7 +24839,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="164"/>
+    <x v="163"/>
     <x v="7"/>
     <x v="0"/>
     <x v="22"/>
@@ -27742,7 +24894,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="177"/>
+    <x v="176"/>
     <x v="25"/>
     <x v="21"/>
     <x v="4"/>
@@ -27764,7 +24916,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="165"/>
+    <x v="164"/>
     <x v="11"/>
     <x v="0"/>
     <x v="22"/>
@@ -27841,7 +24993,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="166"/>
+    <x v="165"/>
     <x v="12"/>
     <x v="0"/>
     <x v="22"/>
@@ -27918,7 +25070,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="167"/>
+    <x v="166"/>
     <x v="15"/>
     <x v="0"/>
     <x v="22"/>
@@ -27995,7 +25147,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="168"/>
+    <x v="167"/>
     <x v="16"/>
     <x v="0"/>
     <x v="22"/>
@@ -28072,7 +25224,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="169"/>
+    <x v="168"/>
     <x v="18"/>
     <x v="0"/>
     <x v="22"/>
@@ -28149,7 +25301,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="170"/>
+    <x v="169"/>
     <x v="4"/>
     <x v="0"/>
     <x v="22"/>
@@ -28226,7 +25378,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="171"/>
+    <x v="170"/>
     <x v="6"/>
     <x v="0"/>
     <x v="22"/>
@@ -28303,7 +25455,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="172"/>
+    <x v="171"/>
     <x v="7"/>
     <x v="0"/>
     <x v="22"/>
@@ -28380,7 +25532,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="173"/>
+    <x v="172"/>
     <x v="10"/>
     <x v="0"/>
     <x v="22"/>
@@ -28457,7 +25609,7 @@
     <x v="1"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="174"/>
+    <x v="173"/>
     <x v="12"/>
     <x v="0"/>
     <x v="22"/>
@@ -28534,7 +25686,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="175"/>
+    <x v="174"/>
     <x v="3"/>
     <x v="0"/>
     <x v="22"/>
@@ -28611,7 +25763,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="176"/>
+    <x v="175"/>
     <x v="6"/>
     <x v="0"/>
     <x v="22"/>
@@ -28688,7 +25840,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="177"/>
+    <x v="176"/>
     <x v="9"/>
     <x v="0"/>
     <x v="22"/>
@@ -28765,7 +25917,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="178"/>
+    <x v="177"/>
     <x v="12"/>
     <x v="0"/>
     <x v="22"/>
@@ -28842,7 +25994,7 @@
     <x v="2"/>
     <x v="10"/>
     <x v="10"/>
-    <x v="179"/>
+    <x v="178"/>
     <x v="4"/>
     <x v="0"/>
     <x v="22"/>
@@ -28919,7 +26071,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="180"/>
+    <x v="179"/>
     <x v="1"/>
     <x v="0"/>
     <x v="22"/>
@@ -28996,7 +26148,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="181"/>
+    <x v="180"/>
     <x v="4"/>
     <x v="0"/>
     <x v="22"/>
@@ -29073,7 +26225,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="182"/>
+    <x v="181"/>
     <x v="7"/>
     <x v="0"/>
     <x v="22"/>
@@ -29150,7 +26302,7 @@
     <x v="1"/>
     <x v="6"/>
     <x v="3"/>
-    <x v="183"/>
+    <x v="182"/>
     <x v="11"/>
     <x v="0"/>
     <x v="22"/>
@@ -29227,7 +26379,7 @@
     <x v="1"/>
     <x v="5"/>
     <x v="0"/>
-    <x v="184"/>
+    <x v="183"/>
     <x v="1"/>
     <x v="0"/>
     <x v="22"/>
@@ -29304,7 +26456,7 @@
     <x v="1"/>
     <x v="5"/>
     <x v="0"/>
-    <x v="185"/>
+    <x v="184"/>
     <x v="2"/>
     <x v="0"/>
     <x v="22"/>
@@ -29381,7 +26533,7 @@
     <x v="1"/>
     <x v="5"/>
     <x v="0"/>
-    <x v="186"/>
+    <x v="185"/>
     <x v="4"/>
     <x v="0"/>
     <x v="22"/>
@@ -29458,7 +26610,7 @@
     <x v="1"/>
     <x v="5"/>
     <x v="0"/>
-    <x v="187"/>
+    <x v="186"/>
     <x v="6"/>
     <x v="0"/>
     <x v="22"/>
@@ -29516,6 +26668,110 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="0" compactData="0">
+  <location ref="A3:C10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="75">
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField axis="axisCol" compact="0" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="62"/>
+  </rowFields>
+  <colFields count="1">
+    <field x="24"/>
+  </colFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="DataPilot1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="0" compactData="0">
   <location ref="A4:D41" firstHeaderRow="1" firstDataRow="1" firstDataCol="3" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="75">
@@ -29684,113 +26940,15 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="1" outlineData="1" compact="0" compactData="0">
-  <location ref="A3:C10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="75">
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField axis="axisCol" compact="0" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="62"/>
-  </rowFields>
-  <colFields count="1">
-    <field x="24"/>
-  </colFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:BW217" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:BW217"/>
+  <autoFilter ref="A1:BW217">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="DSM 9790"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="75">
     <tableColumn id="1" name="sampleName"/>
     <tableColumn id="2" name="Strains"/>
@@ -29876,7 +27034,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A3:C18"/>
+  <dimension ref="A3:C10"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
@@ -29946,46 +27104,6 @@
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="18"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0"/>
-      <c r="B11" s="0"/>
-      <c r="C11" s="0"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0"/>
-      <c r="B12" s="0"/>
-      <c r="C12" s="0"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0"/>
-      <c r="B13" s="0"/>
-      <c r="C13" s="0"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0"/>
-      <c r="B14" s="0"/>
-      <c r="C14" s="0"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0"/>
-      <c r="B15" s="0"/>
-      <c r="C15" s="0"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0"/>
-      <c r="B16" s="0"/>
-      <c r="C16" s="0"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0"/>
-      <c r="B17" s="0"/>
-      <c r="C17" s="0"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0"/>
-      <c r="B18" s="0"/>
-      <c r="C18" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -30231,7 +27349,7 @@
       <c r="B23" s="23"/>
       <c r="C23" s="24"/>
       <c r="D23" s="25" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30241,7 +27359,7 @@
       </c>
       <c r="C24" s="26"/>
       <c r="D24" s="27" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30251,7 +27369,7 @@
         <v>21</v>
       </c>
       <c r="D25" s="30" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30411,7 +27529,7 @@
       <c r="B41" s="32"/>
       <c r="C41" s="33"/>
       <c r="D41" s="18" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -32494,7 +29612,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="37" t="s">
         <v>381</v>
       </c>
@@ -32690,7 +29808,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="37" t="s">
         <v>403</v>
       </c>
@@ -32886,7 +30004,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="37" t="s">
         <v>406</v>
       </c>
@@ -33082,7 +30200,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="37" t="s">
         <v>408</v>
       </c>
@@ -33278,7 +30396,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="37" t="s">
         <v>411</v>
       </c>
@@ -33474,7 +30592,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="37" t="s">
         <v>413</v>
       </c>
@@ -33670,7 +30788,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="37" t="s">
         <v>415</v>
       </c>
@@ -33866,7 +30984,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="37" t="s">
         <v>418</v>
       </c>
@@ -34062,7 +31180,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="37" t="s">
         <v>420</v>
       </c>
@@ -34258,7 +31376,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="37" t="s">
         <v>422</v>
       </c>
@@ -34454,7 +31572,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
         <v>425</v>
       </c>
@@ -34650,7 +31768,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="37" t="s">
         <v>427</v>
       </c>
@@ -34846,7 +31964,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="37" t="s">
         <v>429</v>
       </c>
@@ -35042,7 +32160,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="37" t="s">
         <v>432</v>
       </c>
@@ -35238,7 +32356,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
         <v>434</v>
       </c>
@@ -35434,7 +32552,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
         <v>436</v>
       </c>
@@ -35630,7 +32748,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="37" t="s">
         <v>440</v>
       </c>
@@ -35826,7 +32944,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
         <v>442</v>
       </c>
@@ -36022,7 +33140,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="37" t="s">
         <v>444</v>
       </c>
@@ -36220,7 +33338,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
         <v>450</v>
       </c>
@@ -36418,7 +33536,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="37" t="s">
         <v>452</v>
       </c>
@@ -36616,7 +33734,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
         <v>454</v>
       </c>
@@ -36818,7 +33936,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="37" t="s">
         <v>467</v>
       </c>
@@ -37020,7 +34138,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="37" t="s">
         <v>469</v>
       </c>
@@ -37222,7 +34340,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="37" t="s">
         <v>471</v>
       </c>
@@ -37424,7 +34542,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
         <v>473</v>
       </c>
@@ -37626,7 +34744,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="37" t="s">
         <v>475</v>
       </c>
@@ -37828,7 +34946,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="37" t="s">
         <v>477</v>
       </c>
@@ -38030,7 +35148,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="37" t="s">
         <v>479</v>
       </c>
@@ -38236,7 +35354,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="37" t="s">
         <v>482</v>
       </c>
@@ -38442,7 +35560,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="37" t="s">
         <v>484</v>
       </c>
@@ -38648,7 +35766,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="37" t="s">
         <v>486</v>
       </c>
@@ -38854,7 +35972,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="37" t="s">
         <v>494</v>
       </c>
@@ -39060,7 +36178,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="37" t="s">
         <v>496</v>
       </c>
@@ -39266,7 +36384,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="37" t="s">
         <v>499</v>
       </c>
@@ -39468,7 +36586,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="37" t="s">
         <v>501</v>
       </c>
@@ -39670,7 +36788,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="37" t="s">
         <v>503</v>
       </c>
@@ -39876,7 +36994,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="37" t="s">
         <v>505</v>
       </c>
@@ -40082,7 +37200,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="37" t="s">
         <v>507</v>
       </c>
@@ -40288,7 +37406,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
         <v>509</v>
       </c>
@@ -40490,7 +37608,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
         <v>511</v>
       </c>
@@ -40692,7 +37810,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="37" t="s">
         <v>513</v>
       </c>
@@ -40890,7 +38008,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="37" t="s">
         <v>519</v>
       </c>
@@ -41090,7 +38208,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="37" t="s">
         <v>523</v>
       </c>
@@ -41290,7 +38408,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="37" t="s">
         <v>525</v>
       </c>
@@ -41496,7 +38614,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="37" t="s">
         <v>528</v>
       </c>
@@ -41702,7 +38820,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="37" t="s">
         <v>530</v>
       </c>
@@ -41908,7 +39026,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="37" t="s">
         <v>532</v>
       </c>
@@ -42110,7 +39228,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="37" t="s">
         <v>534</v>
       </c>
@@ -42312,7 +39430,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="37" t="s">
         <v>536</v>
       </c>
@@ -42512,7 +39630,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="37" t="s">
         <v>538</v>
       </c>
@@ -42718,7 +39836,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="37" t="s">
         <v>541</v>
       </c>
@@ -42924,7 +40042,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="37" t="s">
         <v>543</v>
       </c>
@@ -43130,7 +40248,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="37" t="s">
         <v>545</v>
       </c>
@@ -43332,7 +40450,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="37" t="s">
         <v>547</v>
       </c>
@@ -43534,7 +40652,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="37" t="s">
         <v>550</v>
       </c>
@@ -43732,7 +40850,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="37" t="s">
         <v>552</v>
       </c>
@@ -43932,7 +41050,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="37" t="s">
         <v>554</v>
       </c>
@@ -44132,7 +41250,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
         <v>556</v>
       </c>
@@ -44354,7 +41472,7 @@
       <c r="CD60" s="71"/>
       <c r="CE60" s="71"/>
     </row>
-    <row r="61" s="71" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" s="71" customFormat="true" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="49" t="s">
         <v>568</v>
       </c>
@@ -44570,7 +41688,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="62" s="71" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" s="71" customFormat="true" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="49" t="s">
         <v>572</v>
       </c>
@@ -44776,7 +41894,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="63" s="71" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" s="71" customFormat="true" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
         <v>575</v>
       </c>
@@ -44984,7 +42102,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="64" s="71" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" s="71" customFormat="true" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
         <v>578</v>
       </c>
@@ -45190,7 +42308,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="65" s="71" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" s="71" customFormat="true" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="49" t="s">
         <v>583</v>
       </c>
@@ -45396,7 +42514,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="66" s="71" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" s="71" customFormat="true" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="49" t="s">
         <v>586</v>
       </c>
@@ -45602,7 +42720,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="67" s="71" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" s="71" customFormat="true" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="49" t="s">
         <v>590</v>
       </c>
@@ -45808,7 +42926,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="68" s="71" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" s="71" customFormat="true" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="37" t="s">
         <v>592</v>
       </c>
@@ -46005,16 +43123,16 @@
       <c r="BW68" s="37" t="s">
         <v>402</v>
       </c>
-      <c r="BX68" s="0"/>
-      <c r="BY68" s="0"/>
-      <c r="BZ68" s="0"/>
-      <c r="CA68" s="0"/>
+      <c r="BX68" s="1"/>
+      <c r="BY68" s="1"/>
+      <c r="BZ68" s="1"/>
+      <c r="CA68" s="1"/>
       <c r="CB68" s="1"/>
-      <c r="CC68" s="0"/>
+      <c r="CC68" s="1"/>
       <c r="CD68" s="1"/>
       <c r="CE68" s="1"/>
     </row>
-    <row r="69" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="37" t="s">
         <v>599</v>
       </c>
@@ -46212,7 +43330,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="37" t="s">
         <v>601</v>
       </c>
@@ -46410,7 +43528,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="37" t="s">
         <v>603</v>
       </c>
@@ -46608,7 +43726,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="37" t="s">
         <v>605</v>
       </c>
@@ -46812,7 +43930,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="37" t="s">
         <v>610</v>
       </c>
@@ -47016,7 +44134,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="37" t="s">
         <v>612</v>
       </c>
@@ -47220,7 +44338,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="37" t="s">
         <v>614</v>
       </c>
@@ -47424,7 +44542,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="37" t="s">
         <v>616</v>
       </c>
@@ -47628,7 +44746,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="37" t="s">
         <v>618</v>
       </c>
@@ -47832,7 +44950,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="37" t="s">
         <v>620</v>
       </c>
@@ -48028,7 +45146,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="37" t="s">
         <v>623</v>
       </c>
@@ -48224,7 +45342,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="37" t="s">
         <v>625</v>
       </c>
@@ -48420,7 +45538,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="37" t="s">
         <v>627</v>
       </c>
@@ -48616,7 +45734,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="37" t="s">
         <v>629</v>
       </c>
@@ -48812,7 +45930,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="37" t="s">
         <v>631</v>
       </c>
@@ -49008,7 +46126,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="37" t="s">
         <v>633</v>
       </c>
@@ -49204,7 +46322,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="37" t="s">
         <v>635</v>
       </c>
@@ -49400,7 +46518,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="37" t="s">
         <v>637</v>
       </c>
@@ -49596,7 +46714,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="37" t="s">
         <v>639</v>
       </c>
@@ -49792,7 +46910,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="37" t="s">
         <v>641</v>
       </c>
@@ -49996,7 +47114,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="37" t="s">
         <v>645</v>
       </c>
@@ -50200,7 +47318,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="37" t="s">
         <v>648</v>
       </c>
@@ -50404,7 +47522,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="37" t="s">
         <v>650</v>
       </c>
@@ -50608,7 +47726,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="37" t="s">
         <v>652</v>
       </c>
@@ -50812,7 +47930,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="37" t="s">
         <v>654</v>
       </c>
@@ -51016,7 +48134,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="37" t="s">
         <v>656</v>
       </c>
@@ -51220,7 +48338,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="37" t="s">
         <v>658</v>
       </c>
@@ -51424,7 +48542,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="37" t="s">
         <v>660</v>
       </c>
@@ -51628,7 +48746,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="37" t="s">
         <v>662</v>
       </c>
@@ -51832,7 +48950,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="37" t="s">
         <v>664</v>
       </c>
@@ -52036,7 +49154,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="37" t="s">
         <v>666</v>
       </c>
@@ -52240,7 +49358,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="37" t="s">
         <v>668</v>
       </c>
@@ -52444,7 +49562,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="37" t="s">
         <v>670</v>
       </c>
@@ -52650,7 +49768,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="37" t="s">
         <v>679</v>
       </c>
@@ -52856,7 +49974,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="37" t="s">
         <v>682</v>
       </c>
@@ -53062,7 +50180,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="37" t="s">
         <v>685</v>
       </c>
@@ -53266,7 +50384,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="37" t="s">
         <v>692</v>
       </c>
@@ -53468,7 +50586,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="37" t="s">
         <v>695</v>
       </c>
@@ -53670,7 +50788,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="37" t="s">
         <v>699</v>
       </c>
@@ -53868,7 +50986,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="37" t="s">
         <v>706</v>
       </c>
@@ -54062,7 +51180,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="37" t="s">
         <v>708</v>
       </c>
@@ -54260,7 +51378,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="28.35" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="37" t="s">
         <v>711</v>
       </c>
@@ -54464,7 +51582,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="28.35" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="37" t="s">
         <v>719</v>
       </c>
@@ -54656,7 +51774,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="37" t="s">
         <v>726</v>
       </c>
@@ -54854,7 +51972,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="37" t="s">
         <v>731</v>
       </c>
@@ -55046,7 +52164,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="37" t="s">
         <v>737</v>
       </c>
@@ -55239,7 +52357,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="37" t="s">
         <v>744</v>
       </c>
@@ -55444,7 +52562,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="37" t="s">
         <v>753</v>
       </c>
@@ -55649,7 +52767,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="37" t="s">
         <v>755</v>
       </c>
@@ -55854,7 +52972,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="37" t="s">
         <v>757</v>
       </c>
@@ -56059,7 +53177,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="37" t="s">
         <v>759</v>
       </c>
@@ -56254,7 +53372,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="37" t="s">
         <v>762</v>
       </c>
@@ -56455,7 +53573,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="37" t="s">
         <v>764</v>
       </c>
@@ -56650,7 +53768,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="37" t="s">
         <v>766</v>
       </c>
@@ -56849,7 +53967,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="37" t="s">
         <v>768</v>
       </c>
@@ -57044,7 +54162,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="37" t="s">
         <v>771</v>
       </c>
@@ -57239,7 +54357,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="37" t="s">
         <v>773</v>
       </c>
@@ -57434,7 +54552,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="37" t="s">
         <v>775</v>
       </c>
@@ -57629,7 +54747,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="37" t="s">
         <v>777</v>
       </c>
@@ -57824,7 +54942,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="37" t="s">
         <v>779</v>
       </c>
@@ -63131,7 +60249,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="37" t="s">
         <v>843</v>
       </c>
@@ -63336,7 +60454,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="37" t="s">
         <v>853</v>
       </c>
@@ -63541,7 +60659,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="37" t="s">
         <v>855</v>
       </c>
@@ -63746,7 +60864,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="37" t="s">
         <v>857</v>
       </c>
@@ -63951,7 +61069,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="37" t="s">
         <v>859</v>
       </c>
@@ -64156,7 +61274,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="37" t="s">
         <v>861</v>
       </c>
@@ -64361,7 +61479,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="37" t="s">
         <v>863</v>
       </c>
@@ -64566,7 +61684,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="37" t="s">
         <v>865</v>
       </c>
@@ -64771,7 +61889,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="37" t="s">
         <v>867</v>
       </c>
@@ -64976,7 +62094,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="37" t="s">
         <v>869</v>
       </c>
@@ -65181,7 +62299,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="37" t="s">
         <v>871</v>
       </c>
@@ -65386,7 +62504,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="37" t="s">
         <v>873</v>
       </c>
@@ -65591,7 +62709,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="37" t="s">
         <v>875</v>
       </c>
@@ -65790,7 +62908,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="37" t="s">
         <v>882</v>
       </c>
@@ -65989,7 +63107,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="37" t="s">
         <v>884</v>
       </c>
@@ -66188,7 +63306,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="37" t="s">
         <v>886</v>
       </c>
@@ -66387,7 +63505,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="37" t="s">
         <v>888</v>
       </c>
@@ -66586,7 +63704,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="37" t="s">
         <v>890</v>
       </c>
@@ -66785,7 +63903,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="37" t="s">
         <v>892</v>
       </c>
@@ -66984,7 +64102,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="37" t="s">
         <v>894</v>
       </c>
@@ -67183,7 +64301,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="37" t="s">
         <v>896</v>
       </c>
@@ -67382,7 +64500,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="37" t="s">
         <v>898</v>
       </c>
@@ -67585,7 +64703,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="37" t="s">
         <v>900</v>
       </c>
@@ -67788,7 +64906,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="37" t="s">
         <v>902</v>
       </c>
@@ -67991,7 +65109,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="37" t="s">
         <v>904</v>
       </c>
@@ -68194,7 +65312,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="37" t="s">
         <v>906</v>
       </c>
@@ -68385,7 +65503,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="37" t="s">
         <v>913</v>
       </c>
@@ -68588,7 +65706,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="37" t="s">
         <v>915</v>
       </c>
@@ -68791,7 +65909,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="37" t="s">
         <v>917</v>
       </c>
@@ -68994,7 +66112,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="37" t="s">
         <v>919</v>
       </c>
@@ -69197,7 +66315,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="37" t="s">
         <v>922</v>
       </c>
@@ -69400,7 +66518,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="37" t="s">
         <v>931</v>
       </c>
@@ -69603,7 +66721,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="37" t="s">
         <v>933</v>
       </c>
@@ -69806,7 +66924,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="37" t="s">
         <v>935</v>
       </c>
@@ -70009,7 +67127,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
         <v>937</v>
       </c>
@@ -70200,7 +67318,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
         <v>946</v>
       </c>
@@ -70391,7 +67509,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
         <v>948</v>
       </c>
@@ -70582,7 +67700,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
         <v>950</v>
       </c>
@@ -70773,7 +67891,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
         <v>952</v>
       </c>
@@ -70964,7 +68082,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
         <v>954</v>
       </c>
@@ -71155,7 +68273,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
         <v>956</v>
       </c>
@@ -71346,7 +68464,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
         <v>958</v>
       </c>
@@ -71537,7 +68655,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
         <v>960</v>
       </c>
@@ -71728,7 +68846,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
         <v>962</v>
       </c>
@@ -71919,7 +69037,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
         <v>964</v>
       </c>
@@ -72110,7 +69228,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
         <v>967</v>
       </c>
@@ -72301,7 +69419,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
         <v>969</v>
       </c>
@@ -72492,7 +69610,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
         <v>971</v>
       </c>
@@ -72683,7 +69801,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
         <v>973</v>
       </c>
@@ -72874,7 +69992,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
         <v>975</v>
       </c>
@@ -73065,7 +70183,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
         <v>977</v>
       </c>
@@ -73256,7 +70374,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
         <v>979</v>
       </c>
@@ -73447,7 +70565,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
         <v>981</v>
       </c>
@@ -73638,7 +70756,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
         <v>983</v>
       </c>
@@ -73829,7 +70947,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
         <v>985</v>
       </c>
@@ -74013,7 +71131,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
         <v>987</v>
       </c>
@@ -74197,7 +71315,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="s">
         <v>989</v>
       </c>
@@ -74381,7 +71499,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="1" t="s">
         <v>991</v>
       </c>
@@ -74565,7 +71683,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="1" t="s">
         <v>993</v>
       </c>
@@ -74749,7 +71867,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="1" t="s">
         <v>995</v>
       </c>
@@ -74933,7 +72051,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="1" t="s">
         <v>997</v>
       </c>
@@ -75117,7 +72235,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="s">
         <v>999</v>
       </c>
@@ -75301,7 +72419,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="14.9" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="s">
         <v>1001</v>
       </c>
